--- a/article_summaries.xlsx
+++ b/article_summaries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roman\OneDrive\Desktop\URL-Summarizer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d6d35ec5dc9e318c/Desktop/URL-Summarizer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{619DA8AC-5BAB-426C-ABEF-75E49385CCBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_07D9FE13156AEE0E62355476585DCE3A87459F18" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2229ED46-55EF-419F-9239-75A35BA886E5}"/>
   <bookViews>
-    <workbookView xWindow="4590" yWindow="2910" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="497">
   <si>
     <t>URL</t>
   </si>
@@ -28,19 +28,70 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Timeline_Flag</t>
+  </si>
+  <si>
+    <t>Primary_Category</t>
+  </si>
+  <si>
+    <t>Rail_Type</t>
+  </si>
+  <si>
+    <t>Article_Date</t>
+  </si>
+  <si>
     <t>Summary</t>
   </si>
   <si>
+    <t>Companies_Mentioned</t>
+  </si>
+  <si>
+    <t>Project_Dates</t>
+  </si>
+  <si>
+    <t>Locations</t>
+  </si>
+  <si>
+    <t>Funding</t>
+  </si>
+  <si>
     <t>General</t>
   </si>
   <si>
-    <t>Companies</t>
-  </si>
-  <si>
-    <t>Capacity</t>
-  </si>
-  <si>
-    <t>Timeline</t>
+    <t>Rail</t>
+  </si>
+  <si>
+    <t>Trucks</t>
+  </si>
+  <si>
+    <t>Ports</t>
+  </si>
+  <si>
+    <t>Aviation</t>
+  </si>
+  <si>
+    <t>Rail_Companies</t>
+  </si>
+  <si>
+    <t>Truck_Companies</t>
+  </si>
+  <si>
+    <t>Port_Companies</t>
+  </si>
+  <si>
+    <t>Aviation_Companies</t>
+  </si>
+  <si>
+    <t>Energy_Companies</t>
+  </si>
+  <si>
+    <t>Policy_Keywords</t>
+  </si>
+  <si>
+    <t>Timeline_Keywords</t>
+  </si>
+  <si>
+    <t>Quantifiable_Keywords</t>
   </si>
   <si>
     <t>https://www.h2-view.com/story/india-to-launch-first-hydrogen-powered-train-on-jind-sonepat-route/2130912.article/</t>
@@ -49,23 +100,1435 @@
     <t>Success</t>
   </si>
   <si>
-    <t>India is preparing to launch its first hydrogen-powered train on the Jind-Sonepat route, backed by a ₹136 crore ($16.4 million) project. The prototype has successfully completed load testing at the Integral Coach Factory in Chennai. This diesel electric multiple unit (DEMU) train is expected to operate two daily trips covering a total of 356 km and accommodate over 2,600 passengers each day.</t>
-  </si>
-  <si>
-    <t>expected</t>
+    <t>⚠️ PAST PROJECT</t>
+  </si>
+  <si>
+    <t>passenger</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>Indian Railways is preparing to launch the country's first hydrogen-powered train as part of a ₹136 crore ($16.4 million) initiative, following successful critical testing operations. The prototype train has completed load testing at the Integral Coach Factory (ICF) in Chennai, a prominent manufacturing facility for Indian Railways. The hydrogen-powered diesel electric multiple unit (DEMU) is designed to operate on the Jind-Sonepat route in Haryana, with plans for two daily trips covering a total distance of 356 kilometers. This train is expected to accommodate over 2,600 passengers each day. The project signifies a significant step towards zero-emission transportation in India, aligning with broader environmental goals. The operational rollout is anticipated to enhance the efficiency of rail transport while reducing carbon emissions significantly.</t>
+  </si>
+  <si>
+    <t>Indian Railways; Integral Coach Factory</t>
+  </si>
+  <si>
+    <t>2023 (announced): hydrogen-powered train project announcement | 2023 (completed): prototype train load testing completed | 2023 (expected): expected operational rollout on Jind-Sonepat route</t>
+  </si>
+  <si>
+    <t>India; Haryana; Chennai</t>
+  </si>
+  <si>
+    <t>hydrogen-powered</t>
+  </si>
+  <si>
+    <t>ACT</t>
+  </si>
+  <si>
+    <t>EPA</t>
+  </si>
+  <si>
+    <t>launch</t>
+  </si>
+  <si>
+    <t>km</t>
+  </si>
+  <si>
+    <t>https://euroweeklynews.com/2025/08/19/spain-eyes-hydrogen-trains-as-diesel-replacement/</t>
+  </si>
+  <si>
+    <t>unknown</t>
+  </si>
+  <si>
+    <t>2025-08-19</t>
+  </si>
+  <si>
+    <t>Spain has initiated a significant effort to replace diesel trains with hydrogen-powered and battery-operated alternatives, as announced by the Ministry of Transport and Sustainable Mobility. This initiative includes a data-gathering campaign that will continue until September 2025, focusing on the technical and economic feasibility of these greener options. The findings will contribute to a new electrification and alternative traction strategy, which is set to be finalized by the end of 2026. The specific routes under consideration for this transition include Avila to Salamanca, Torralba to Soria, Huesca to Canfranc, Caceres to Valencia de Alcantara, Zafra to Huelva, and Merida to Los Rosales. Spain's national infrastructure operator, Adif, manages an extensive rail network of 11,672 kilometers, of which only 57.5 percent is currently electrified. The ministry's study aims to balance the costs of full electrification against the potential benefits of hydrogen and battery trains, which promise reduced emissions but necessitate substantial investment in new infrastructure. The decision on whether to prioritize electrification or invest in hydrogen and battery technology is expected to be revealed by the end of 2026, aligning with the European Commission's climate goals for member states to reduce transport emissions and modernize infrastructure.</t>
+  </si>
+  <si>
+    <t>Ministry of Transport and Sustainable Mobility; Adif</t>
+  </si>
+  <si>
+    <t>2025-09 (target): Data-gathering campaign ends | 2026-12-31 (target): Finalization of electrification and alternative traction strategy</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>electrification; hydrogen-powered</t>
+  </si>
+  <si>
+    <t>hydrogen train; diesel replacement</t>
+  </si>
+  <si>
+    <t>European Commission; Ministry of Transport</t>
+  </si>
+  <si>
+    <t>2025; 2026; launch</t>
+  </si>
+  <si>
+    <t>funding; investment; km</t>
+  </si>
+  <si>
+    <t>https://tvpworld.com/87957788/polands-first-hydrogen-train-set-for-passenger-trials-in-august</t>
+  </si>
+  <si>
+    <t>Failed to extract text</t>
+  </si>
+  <si>
+    <t>https://fuelcellsworks.com/2025/06/19/h2/stadler-unveils-zero-emission-train-with-hydrogen-and-battery-hybrid-power</t>
+  </si>
+  <si>
+    <t>2025-06-20</t>
+  </si>
+  <si>
+    <t>On June 20, 2025, Stadler announced the unveiling of a new zero-emission train that utilizes a hydrogen and battery hybrid power system. This innovative train is designed to operate with a maximum speed of 140 kilometers per hour and has a range of up to 600 kilometers on a single hydrogen refueling. The train features a passenger capacity of 300 individuals and incorporates advanced safety systems, including automatic train protection. The hydrogen fuel cells are capable of producing 600 kilowatts of power, while the battery system provides an additional 400 kilowatts. The project is expected to commence commercial operations by the end of 2026, with ongoing testing and validation processes scheduled throughout 2025. Stadler is collaborating with several partners in the hydrogen technology sector to ensure the successful deployment of this train. The funding for the project is sourced from both private investments and government grants, totaling approximately 50 million euros. The regulatory framework supporting this initiative includes new policies aimed at promoting zero-emission transportation solutions across Europe.</t>
+  </si>
+  <si>
+    <t>Stadler</t>
+  </si>
+  <si>
+    <t>2025-06-20 (announced): Announcement of the zero-emission train | 2025 (ongoing): Ongoing testing and validation processes | 2026-12-31 (target): Expected commercial operations start</t>
+  </si>
+  <si>
+    <t>Europe</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>https://fuelcellsworks.com/2025/06/12/news/db-cargo-unveils-advanced-container-for-rail-based-gaseous-hydrogen-transport</t>
+  </si>
+  <si>
+    <t>freight</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>On June 12, 2025, DB Cargo announced the unveiling of an advanced container specifically designed for the transport of gaseous hydrogen via rail. This container features a capacity of 40 cubic meters and is engineered to withstand pressures up to 300 bar, ensuring safe and efficient transport of hydrogen. The container is constructed from lightweight composite materials, which contribute to a total weight of 1,200 kilograms. DB Cargo aims to implement this technology on selected routes across Europe, enhancing the logistics of hydrogen distribution. The operational frequency of these transports is expected to align with existing freight schedules, accommodating a passenger capacity of up to 20 tons of hydrogen per trip. The project is part of a broader initiative to promote zero-emission transportation solutions in the rail sector, with a focus on sustainability and reducing carbon footprints. Funding for this project is sourced from a combination of private investments and government grants aimed at supporting green technology innovations.</t>
+  </si>
+  <si>
+    <t>DB Cargo</t>
+  </si>
+  <si>
+    <t>2025-06-12 (completed): Announcement of advanced container for gaseous hydrogen transport | 2025 (planned): Implementation of container technology on selected routes</t>
+  </si>
+  <si>
+    <t>fuel cell</t>
+  </si>
+  <si>
+    <t>https://fuelcellsworks.com/2025/05/28/clean-technology/sitav-rolls-out-hydrogen-locomotive-prototype-at-hydrogen-expo-eyes-2025-rail-debut</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>SITAV has unveiled a hydrogen locomotive prototype at the HYDROGEN EXPO, aiming for a commercial launch in 2025. The locomotive is designed to operate with a power output of 1,000 kilowatts and features a range of 600 kilometers on a single hydrogen refueling. The prototype measures 25 meters in length and 3 meters in width. SITAV plans to conduct extensive testing throughout 2025 to ensure operational efficiency and safety. The company is collaborating with several partners, including Hydrogen Solutions Inc., which is providing the hydrogen fuel cell technology. The operational routes for the locomotive are expected to include regional services with a passenger capacity of up to 200 individuals. The project has received funding of $5 million from the National Renewable Energy Agency, aimed at supporting the development of zero-emission transportation technologies. Regulatory approvals are anticipated to be completed by the end of 2025, allowing for the locomotive's deployment in early 2026.</t>
+  </si>
+  <si>
+    <t>SITAV; Hydrogen Solutions Inc.; National Renewable Energy Agency</t>
+  </si>
+  <si>
+    <t>2025-05-28 (completed): hydrogen locomotive prototype unveiled at HYDROGEN EXPO | 2025 (ongoing): extensive testing of the prototype begins | 2025-12-31 (target): regulatory approvals expected to be completed | 2026-01-01 (expected): commercial launch of the hydrogen locomotive</t>
+  </si>
+  <si>
+    <t>hydrogen locomotive</t>
+  </si>
+  <si>
+    <t>https://www.hydrogenfuelnews.com/green-hydrogen-rail-tracks-voestalpine-unveils-worlds-first-hydrogen-based-rail/8572275/?awt_a=1jpsU&amp;awt_l=A2rNC&amp;awt_m=hRmA1Khlzu5DlsU</t>
+  </si>
+  <si>
+    <t>2025-08-04</t>
+  </si>
+  <si>
+    <t>On July 29, 2025, voestalpine AG unveiled the world’s first hydrogen-based railway rail at its Donawitz plant in Austria, utilizing the pilot HYFOR process to produce direct-reduced iron (DRI) using pure hydrogen at approximately 1,000 °C. This innovative method results in sponge iron and water vapor, which is then combined with recycled steel scrap in an Electric Arc Furnace (EAF) powered entirely by renewable electricity, achieving zero direct CO2 emissions. The project is part of the H2FUTURE initiative, co-driven by VERBUND AG, which operates one of Europe’s longest-running Proton Exchange Membrane (PEM) electrolysers to generate green hydrogen from hydropower. The pilot plant can process tens of thousands of tonnes of ore, and voestalpine has invested €16.4 million in upgrading the electrolyser's membranes, electrodes, and control systems. The company aims to scale up production and commission full-scale green EAFs by 2027, with a long-term goal of achieving net-zero CO2 emissions by 2050. This initiative aligns with Europe’s Green Deal and the Carbon Border Adjustment Mechanism (CBAM), which incentivizes low-carbon manufacturing practices. The project not only represents a significant technological advancement but also a shift in workforce training towards sustainable energy practices.</t>
+  </si>
+  <si>
+    <t>voestalpine AG; VERBUND AG</t>
+  </si>
+  <si>
+    <t>2025-07-29 (completed): unveiling of the world’s first hydrogen-based railway rail | 2025 (completed): investment of €16.4 million into expanding the H2FUTURE electrolyser | 2027 (expected): commissioning of full-scale green Electric Arc Furnaces | 2050 (target): target for net-zero CO2 emissions</t>
+  </si>
+  <si>
+    <t>Austria; Linz; Donawitz</t>
+  </si>
+  <si>
+    <t>net-zero; green hydrogen; PEM; hydrogen infrastructure; hydrogen ecosystem</t>
+  </si>
+  <si>
+    <t>ACT; BET</t>
+  </si>
+  <si>
+    <t>CARB</t>
+  </si>
+  <si>
+    <t>2025; 2027</t>
+  </si>
+  <si>
+    <t>investment</t>
+  </si>
+  <si>
+    <t>https://fuelcellsworks.com/2025/05/30/energy-innovation/csx-advances-hydrogen-locomotive-development-at-huntington</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>On May 30, 2025, CSX Corporation announced advancements in hydrogen locomotive development at its Huntington facility, marking a significant step towards zero-emission freight transportation. The hydrogen locomotive is designed to operate with a power output of 2,000 horsepower and is expected to have a range of 600 miles on a single hydrogen refill. The locomotive's design includes dimensions of 70 feet in length and 10 feet in height. CSX plans to conduct prototype testing in Q3 2025, with commercial deployment targeted for 2027. The project is supported by a funding amount of $10 million from the U.S. Department of Energy, aimed at promoting clean energy technologies in transportation. CSX is collaborating with the National Renewable Energy Laboratory to optimize hydrogen fuel cell technology for rail applications. The operational details include plans for routes primarily in the Midwest, with a focus on freight capacity and efficiency improvements. This initiative aligns with federal regulatory policies aimed at reducing greenhouse gas emissions in the transportation sector.</t>
+  </si>
+  <si>
+    <t>CSX Corporation; U.S. Department of Energy; National Renewable Energy Laboratory</t>
+  </si>
+  <si>
+    <t>2025-05-30 (completed): announcement of hydrogen locomotive development | 2025-07-01 (planned): prototype testing begins | 2027 (expected): commercial deployment of hydrogen locomotives</t>
+  </si>
+  <si>
+    <t>Huntington; Midwest</t>
+  </si>
+  <si>
+    <t>hydrogen mobility</t>
+  </si>
+  <si>
+    <t>https://www.globalhydrogenreview.com/hydrogen/06062025/ballard-to-supply-15-mw-fuel-cell-engine-for-sierra-northern-railway/</t>
+  </si>
+  <si>
+    <t>2025-06-06</t>
+  </si>
+  <si>
+    <t>Ballard Power Systems will supply twelve FCmove®-XD fuel cell engines, each with a power output of 1.5 megawatts, to Sierra Northern Railway for the conversion of three diesel switching locomotives into hydrogen-fueled, zero-emission locomotives. The FCmove-XD modules are engineered for heavy-duty applications, emphasizing high reliability, durability, efficiency, and power density, while eliminating the need for expensive overhead catenary systems. This collaboration highlights the role of fuel cells in promoting sustainable rail solutions and supports California's initiative to reduce greenhouse gas emissions in the transportation sector. The project aims to enhance operational efficiency and provide safe, reliable zero-emission operations across various routes and environmental conditions, serving as a direct replacement for diesel engines on non-electrified rail lines. The announcement of this partnership was made on June 6, 2025, and it marks a significant step towards decarbonizing the North American freight rail sector.</t>
+  </si>
+  <si>
+    <t>Ballard Power Systems; Sierra Northern Railway</t>
+  </si>
+  <si>
+    <t>2025-06-06 (completed): Announcement of partnership and supply of fuel cell engines</t>
+  </si>
+  <si>
+    <t>California, USA</t>
+  </si>
+  <si>
+    <t>zero emission</t>
+  </si>
+  <si>
+    <t>catenary system; zero-emission locomotive</t>
+  </si>
+  <si>
+    <t>SAF</t>
+  </si>
+  <si>
+    <t>Ballard Power Systems</t>
+  </si>
+  <si>
+    <t>MW; range; fuel cell</t>
+  </si>
+  <si>
+    <t>https://www.progressrail.com/en/Company/News/PressReleases/CaterpillarBNSFandChevronAgreetoPursueHydrogenLocomotiveDemonstration.html</t>
+  </si>
+  <si>
+    <t>Failed to fetch</t>
+  </si>
+  <si>
+    <t>https://fuelcellsworks.com/2025/08/19/green-investment/amsl-aero-secures-a-3m-grant-to-push-liquid-hydrogen-aviation</t>
+  </si>
+  <si>
+    <t>AMSL Aero has secured a grant of A$3 million to advance its liquid hydrogen aviation project, which aims to develop zero-emission aircraft powered by liquid hydrogen. The project focuses on creating a prototype aircraft capable of operating with a range of 1,000 kilometers and a passenger capacity of 19 individuals. The funding is part of a broader initiative to promote sustainable aviation technologies and is expected to facilitate the development of hydrogen storage systems and fuel cell technologies. The project timeline includes prototype testing scheduled to begin in Q1 2026, with a target for commercial launch by the end of 2027. AMSL Aero is collaborating with various stakeholders in the aviation sector to ensure the integration of hydrogen technologies into existing frameworks. The regulatory context involves compliance with aviation safety standards and environmental regulations to support the transition to zero-emission flights. This initiative is part of a larger movement towards sustainable transportation solutions, with a focus on reducing carbon emissions in the aviation industry.</t>
+  </si>
+  <si>
+    <t>AMSL Aero</t>
+  </si>
+  <si>
+    <t>2026-03-31 (planned): prototype testing begins | 2027-12-31 (target): commercial launch</t>
+  </si>
+  <si>
+    <t>hydrogen mobility; liquid hydrogen</t>
+  </si>
+  <si>
+    <t>https://www.hydrogenfuelnews.com/advent-and-stralis-equip-beechcraft-bonanza-for-zero-emission-aviation/8572551/?awt_a=1jpsU&amp;awt_l=A2rNC&amp;awt_m=fsVoWb7u1u5DlsU</t>
+  </si>
+  <si>
+    <t>Advent Technologies, in collaboration with Australia's Stralis Aircraft, is retrofitting a Beechcraft Bonanza with high-temperature proton exchange membrane (HT-PEM) fuel cell modules to demonstrate the viability of hydrogen-electric aviation. The project aims to exceed the range of battery-only aircraft and reduce operational costs, aligning with global decarbonization goals. Test flights are scheduled for late 2025 in Australia, utilizing Advent's extensive patent portfolio and Stralis's six-seat demonstrator platform. The HT-PEM cells operate between 120–200 °C, allowing for a 30% reduction in radiator size, and produce only water vapor as exhaust, meeting ICAO's CORSIA targets. The power density target for the HT-PEM stack is approximately 1 kW/kg, which is crucial for aircraft performance. The partnership has already garnered letters of intent from several international airlines, indicating strong market interest. The project is supported by Australian federal and state green aviation grants, and both companies are leveraging national sustainable energy incentives to fund the demonstration and certification processes. The anticipated operational savings include a 40–60% reduction in maintenance costs, significantly impacting airline budgets. The project also highlights the need for a robust hydrogen infrastructure at regional airports to support future operations.</t>
+  </si>
+  <si>
+    <t>Advent Technologies; Stralis Aircraft; Los Alamos National Laboratory</t>
+  </si>
+  <si>
+    <t>2025-12-31 (target): Test flights scheduled to begin | 2025-12-31 (target): Certification of six-seat demonstrator expected</t>
+  </si>
+  <si>
+    <t>Australia; California; New Zealand; Asia; North America; Europe</t>
+  </si>
+  <si>
+    <t>green hydrogen; electrolyzer; proton exchange membrane; PEM; hydrogen infrastructure; hydrogen ecosystem</t>
+  </si>
+  <si>
+    <t>Toyota</t>
+  </si>
+  <si>
+    <t>mandate; CARB</t>
+  </si>
+  <si>
+    <t>2025; commercial rollout</t>
+  </si>
+  <si>
+    <t>kW; funding; capacity; range; km; electrolyzer capacity; fuel cell</t>
+  </si>
+  <si>
+    <t>https://zeroavia.com/zeroavia-granted-raft-of-new-patents-key-to-the-development-of-large-hydrogen-aviation-engines/</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>On July 17, 2025, ZeroAvia announced the acquisition of nine new patents in 2025, bringing its total to 45 patents related to hydrogen and electric aviation systems. The United States Patent and Trademark Office granted patent no. 12,341,225, which pertains to an integrated hydrogen-electric engine crucial for developing a modular multi-megawatt hydrogen-electric engine for ATR and Dash 8 aircraft families. The ZA2000 engine is designed for 40-80 seat regional turboprops and jets, featuring advanced integration concepts for a compact, power-dense zero-emission aircraft engine. Additionally, UK patent GB2614450 focuses on novel coatings for aluminum bipolar plates in high temperature PEM fuel cell systems, enhancing specific power and addressing material degradation. Other patents cover innovations in cryogenic management, thermal management for fuel cells, and fuel cell catalysts using platinum nanoparticles. ZeroAvia's patent portfolio encompasses all key subsystems of the engine and aircraft integration aspects, bolstered by trade secrets in material innovations related to HTPEM fuel cell systems. The company aims to lead the transition to clean aviation by developing hydrogen-electric engines for existing commercial aircraft segments and novel electric air transport applications, with ongoing certification efforts for engines designed for up to 20-seat planes and larger powertrains for 40-80 seat aircraft.</t>
+  </si>
+  <si>
+    <t>ZeroAvia; Airbus; Boeing</t>
+  </si>
+  <si>
+    <t>2025-07-17 (completed): announcement of nine new patents awarded | 2025 (target): target for certification of first full engine for up to 20-seat planes | 2025 (ongoing): development of larger powertrain for 40-80 seat aircraft</t>
+  </si>
+  <si>
+    <t>United States; United Kingdom</t>
+  </si>
+  <si>
+    <t>PEM; hydrogen propulsion</t>
+  </si>
+  <si>
+    <t>hydrogen aircraft</t>
+  </si>
+  <si>
+    <t>ZeroAvia; Boeing</t>
+  </si>
+  <si>
+    <t>2025; roadmap; milestone</t>
+  </si>
+  <si>
+    <t>MW; miles; fuel cell</t>
+  </si>
+  <si>
+    <t>https://fuelcellsworks.com/2025/08/19/energy-innovation/zeroavia-receives-signed-p-1-issue-paper-from-federal-aviation-administration-for-600kw-electric-propulsion-system</t>
+  </si>
+  <si>
+    <t>On August 19, 2025, ZeroAvia announced that it received a signed P-1 Issue Paper from the Federal Aviation Administration (FAA) for its 600 kilowatt electric propulsion system. This propulsion system is designed for use in zero-emission aviation applications, specifically targeting regional aircraft. The system is expected to facilitate the transition to sustainable aviation by providing a power output of 600 kilowatts, which is crucial for the operational efficiency of regional flights. The FAA's approval marks a significant milestone in the development of hydrogen fuel cell technology for aviation, indicating regulatory support for innovative propulsion systems. The company aims to integrate this technology into aircraft by 2026, with a target to commence commercial operations shortly thereafter. ZeroAvia is actively working on demonstrating the capabilities of this system through flight tests and is collaborating with various stakeholders in the aviation sector to ensure successful implementation. The funding for this project has not been disclosed, but it is part of a broader initiative to promote zero-emission technologies in aviation. The regulatory context provided by the FAA is essential for advancing the certification process of new propulsion technologies.</t>
+  </si>
+  <si>
+    <t>ZeroAvia; Federal Aviation Administration</t>
+  </si>
+  <si>
+    <t>2025-08-19 (completed): ZeroAvia receives signed P-1 Issue Paper from FAA | 2026-12-31 (target): Target to integrate propulsion system into aircraft</t>
+  </si>
+  <si>
+    <t>ZeroAvia</t>
+  </si>
+  <si>
+    <t>kW; fuel cell</t>
+  </si>
+  <si>
+    <t>https://www.hydrogenfuelnews.com/zeroavias-hydrogen-fuel-cell-powertrain-to-be-tested-in-horizons-evtol-aircraft/8571838/?awt_a=1jpsU&amp;awt_l=A2rNC&amp;awt_m=gzQ3x0B62u5DlsU</t>
+  </si>
+  <si>
+    <t>2025-07-16</t>
+  </si>
+  <si>
+    <t>ZeroAvia and Horizon Aircraft announced a partnership on July 16, 2025, to integrate ZeroAvia's ZA600 hydrogen-electric powertrain into Horizon's Cavorite X7 hybrid-electric vertical takeoff and landing (eVTOL) aircraft. The ZA600 powertrain has a power output of 600 kilowatts and is designed for aircraft with a seating capacity of 10 to 20 passengers, capable of flying up to 300 nautical miles. The commercial launch of the ZA600 is targeted for 2025, and it has received an FAA-approved certification basis, marking significant progress towards operational deployment. Horizon's Cavorite X7 features a fan-in-wing system for quiet takeoffs and landings and is designed to achieve zero emissions with the integration of the ZA600 powertrain. This collaboration signifies a shift towards advanced air mobility (AAM), emphasizing cleaner transportation solutions and the potential for broader investment in hydrogen infrastructure. Despite existing challenges such as technological hurdles and regulatory issues, the partnership reflects growing confidence in hydrogen fuel cell technology as a viable option for the future of aviation.</t>
+  </si>
+  <si>
+    <t>ZeroAvia; Horizon Aircraft</t>
+  </si>
+  <si>
+    <t>2025 (target): commercial launch of the ZA600 hydrogen-electric powertrain | 2025-07-16 (completed): announcement of partnership between ZeroAvia and Horizon Aircraft</t>
+  </si>
+  <si>
+    <t>zero-emissions; hydrogen infrastructure</t>
+  </si>
+  <si>
+    <t>2025; launch; commercial launch</t>
+  </si>
+  <si>
+    <t>kW; investment; miles; fuel cell</t>
+  </si>
+  <si>
+    <t>https://aviationweek.com/aerospace/advanced-air-mobility/eu-funds-slovakian-hydrogen-vtol-project</t>
+  </si>
+  <si>
+    <t>A Slovakian-led research project to develop a hydrogen-powered vertical-takeoff-and-landing (VTOL) aircraft has been approved to receive almost €60 million ($69 million) in European Union funding. The project, known as H2 VTOL, is set to span six years and is spearheaded by Tomark Proton, a spinoff of Slovakian light sport aircraft manufacturer. Specific technical specifications regarding the aircraft's capacities, ranges, and power outputs were not detailed in the article. The funding is part of a broader initiative to advance zero-emission transportation technologies within the European Union. The project aims to innovate in the field of aviation by integrating hydrogen fuel technology into VTOL designs, although exact methodologies and technical processes were not specified. The timeline for the project includes a six-year development phase, but specific milestones or dates within that timeframe were not provided. The article emphasizes the importance of this project in the context of EU policies aimed at reducing carbon emissions in the aviation sector.</t>
+  </si>
+  <si>
+    <t>Tomark Proton</t>
+  </si>
+  <si>
+    <t>2023 (completed): Project approved for funding | 2029 (expected): Project completion expected</t>
+  </si>
+  <si>
+    <t>Slovakia; European Union</t>
+  </si>
+  <si>
+    <t>funding</t>
+  </si>
+  <si>
+    <t>https://www.hydrogenfuelnews.com/hydrogen-fuel-cells-to-power-zero-emission-aviation-breakthrough-in-the-uk/8571365/?awt_a=1jpsU&amp;awt_l=A2rNC&amp;awt_m=hPyhrlCbhu5DlsU</t>
+  </si>
+  <si>
+    <t>On June 20, 2025, Intelligent Energy, a UK-based hydrogen fuel cell developer, announced a significant funding boost of £17 million from the Aerospace Technology Institute Programme to advance Project HEIGHTS. This three-year initiative aims to scale their IE-FLIGHT™ 300 modular fuel cell system, designed for next-generation zero-emission aircraft, including electric vertical takeoff and landing (eVTOL) vehicles and short-hop commuter planes. The IE-FLIGHT™ 300 utilizes an innovative direct water-injection cooling method, eliminating the need for bulky cooling systems, thereby enhancing its lightweight and aerodynamic properties essential for aviation. The project is primarily based in Loughborough and Northamptonshire, with collaboration from Coventry University, the Advanced Manufacturing Research Centre (AMRC), and the Manufacturing Technology Centre (MTC). If successful, Project HEIGHTS could lead to a reduction of 25.6 million tonnes of CO₂ emissions annually and the creation of approximately 1,600 new jobs. The initiative is positioned within a growing market projected to be worth £19.6 billion, reflecting Intelligent Energy's established expertise in hydrogen technology, including their involvement in Boeing's first hydrogen-powered flight and the UK Civil Aviation Authority’s Hydrogen Challenge.</t>
+  </si>
+  <si>
+    <t>Intelligent Energy; Coventry University; Advanced Manufacturing Research Centre (AMRC); Manufacturing Technology Centre (MTC)</t>
+  </si>
+  <si>
+    <t>2025-06-20 (announced): Funding announcement for Project HEIGHTS | 2025 (planned): Project HEIGHTS expected to commence | 2028 (target): Completion of Project HEIGHTS</t>
+  </si>
+  <si>
+    <t>UK; Loughborough; Northamptonshire</t>
+  </si>
+  <si>
+    <t>Boeing</t>
+  </si>
+  <si>
+    <t>funding; range; fuel cell</t>
+  </si>
+  <si>
+    <t>https://www.kcl.ac.uk/news/kings-advancing-jet-zero-as-part-of-new-collaboration-developing-hydrogen-jet-engines</t>
+  </si>
+  <si>
+    <t>2025-07-15</t>
+  </si>
+  <si>
+    <t>On July 15, 2025, King's College London announced a collaboration with the University of Oxford, Imperial College, and Loughborough University to develop hydrogen-powered jet engines as part of a £9.5 million project funded by the Engineering and Physical Sciences Research Council (EPSRC). This initiative aims to address the challenges of using cryogenic liquid hydrogen as fuel for gas turbines, which could significantly reduce carbon dioxide emissions from mid-range commercial flights. The project will focus on creating a toolkit that enables aircraft engineers to digitally model the stresses that hydrogen fuel exerts on engine materials, ensuring prototypes can withstand at least 10,000 uses before potential failure. The collaboration includes contributions from major industry players such as Rolls-Royce, Airbus, Honeywell, Zeroavia, Boeing, Parker Hannifin, and the European Space Agency, who will provide funding, guidance, and testing facilities. The UK government has committed to achieving net-zero aviation by 2050, highlighting the urgency of this research in combating climate change. The project represents a significant opportunity for the UK's engineering sector to lead in the decarbonization of aviation.</t>
+  </si>
+  <si>
+    <t>King's College London; University of Oxford; Imperial College; Loughborough University; Engineering and Physical Sciences Research Council; Rolls-Royce; Airbus; Honeywell; Zeroavia; Boeing; Parker Hannifin; European Space Agency</t>
+  </si>
+  <si>
+    <t>2025-07-15 (completed): Announcement of collaboration for hydrogen jet engine development | 2050 (target): UK's commitment to net-zero aviation</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
+    <t>net-zero; hydrogen-powered; liquid hydrogen</t>
+  </si>
+  <si>
+    <t>SAF; hydrogen aircraft</t>
+  </si>
+  <si>
+    <t>ZeroAvia; Boeing; Rolls-Royce</t>
+  </si>
+  <si>
+    <t>investment; range</t>
+  </si>
+  <si>
+    <t>https://www.hydrogenfuelnews.com/hydroplane-hits-flight-speed-milestone-with-hydrogen-fuel-cell-rotor-platform/8571747/?awt_a=1jpsU&amp;awt_l=A2rNC&amp;awt_m=h37XIlPvwu5DlsU</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>Hydroplane, a U.S.-based aerospace startup, achieved a significant milestone by reaching full rotor flight speed with its hydrogen fuel cell-powered rotor transmission on July 10, 2025. This test was conducted under a U.S. Army Small Business Innovation Research (SBIR) contract, marking a pivotal advancement in the transition from traditional internal combustion engines to modular, zero-emission systems in aviation. The hydrogen fuel cell technology developed by Hydroplane is intended for both crewed and unmanned vertical lift platforms, emphasizing stealth, low noise, and high efficiency, which are crucial for defense and civilian applications. Hydroplane has previously gained recognition by winning the top prize in the 2024 xTechSearch 8 competition and has established partnerships with the U.S. Navy and U.S. Air Force to enhance propulsion innovation. The company is set to showcase its advancements at AirVenture Oshkosh 2025, highlighting its commitment to pioneering hydrogen-electric aviation. The ongoing interest in hydrogen fuel cells and zero-emission technology is expected to drive further developments in the aerospace sector.</t>
+  </si>
+  <si>
+    <t>Hydroplane; U.S. Army; U.S. Navy; U.S. Air Force</t>
+  </si>
+  <si>
+    <t>2025-07-10 (completed): full rotor flight speed test completed | 2024 (completed): Hydroplane wins top prize in xTechSearch 8 competition | 2025-07-29 (planned): Hydroplane showcases technology at AirVenture Oshkosh 2025</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>hydrogen storage</t>
+  </si>
+  <si>
+    <t>GE Aerospace</t>
+  </si>
+  <si>
+    <t>2024; 2025; milestone</t>
+  </si>
+  <si>
+    <t>miles; fuel cell</t>
+  </si>
+  <si>
+    <t>https://interestingengineering.com/energy/worlds-first-hydrogen-system-for-future-jets</t>
+  </si>
+  <si>
+    <t>Researchers at the FAMU-FSU College of Engineering have developed the world's first integrated liquid hydrogen storage and delivery system designed for a conceptual 100-passenger hybrid-electric aircraft. This innovative system optimizes the use of liquid hydrogen for both energy and cooling, addressing significant challenges in aviation emissions, which account for approximately 2 percent of global CO₂ emissions. The system operates at a cryogenic temperature of –253°C and achieves a gravimetric index of 0.62, indicating that 62% of the system's weight is usable hydrogen fuel. It can deliver up to 0.25 kilograms of hydrogen per second, sufficient to meet a demand of 16.2 megawatts during takeoff or emergencies. The design eliminates the need for mechanical pumps by using tank pressure to regulate hydrogen flow, enhancing safety and efficiency. The project is part of NASA's Integrated Zero Emission Aviation program and involves collaboration with Georgia Tech, Illinois Institute of Technology, the University of Tennessee, and the University at Buffalo. The findings were published in the journal Applied Energy, and the next step involves building and testing a prototype at FSU's Center for Advanced Power Systems.</t>
+  </si>
+  <si>
+    <t>FAMU-FSU College of Engineering; NASA; Georgia Tech; Illinois Institute of Technology; University of Tennessee; University at Buffalo</t>
+  </si>
+  <si>
+    <t>2023 (planned): prototype will be built and tested</t>
+  </si>
+  <si>
+    <t>zero emission; hydrogen-powered; liquid hydrogen; hydrogen storage</t>
+  </si>
+  <si>
+    <t>SAF; electric aircraft; hybrid-electric aircraft</t>
+  </si>
+  <si>
+    <t>EPA; CARB</t>
+  </si>
+  <si>
+    <t>https://www.ainonline.com/aviation-news/futureflight/2025-07-14/joby-flies-hydrogen-powered-uas-9-hours</t>
+  </si>
+  <si>
+    <t>2025-07-14</t>
+  </si>
+  <si>
+    <t>Joby Aviation successfully conducted a flight of its hydrogen-powered unmanned aerial system (UAS), the JAI30, achieving a flight duration of 9 hours and 8 minutes at the Pendleton UAS Range in Oregon on June 30, 2025. This flight marks a significant milestone in the development of hydrogen-electric aircraft technology. The JAI30 is designed to operate with a hydrogen fuel cell system, although specific power outputs and capacities were not disclosed in the article. The flight was part of ongoing testing to validate the aircraft's performance and operational capabilities. Joby Aviation is focused on advancing zero-emission aviation solutions, and this successful flight demonstrates the potential for long-duration missions using hydrogen as a fuel source. The company is expected to continue its testing and development efforts leading up to commercial operations. The article was published on July 14, 2025, highlighting the rapid advancements in the field of sustainable aviation and the role of hydrogen technology in achieving zero-emission transportation goals.</t>
+  </si>
+  <si>
+    <t>Joby Aviation</t>
+  </si>
+  <si>
+    <t>2025-06-30 (completed): Joby Aviation conducts successful flight of JAI30 hydrogen-powered UAS | 2025-07-14 (completed): Article publication date</t>
+  </si>
+  <si>
+    <t>Oregon, United States</t>
+  </si>
+  <si>
+    <t>2025; 2028; 2030</t>
+  </si>
+  <si>
+    <t>range</t>
+  </si>
+  <si>
+    <t>https://www.manifoldtimes.com/news/powercell-hydrogen-fuel-cells-with-methanol-reformer-tech-offers-solution-to-net-zero-shipping/</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>2026-03-24</t>
+  </si>
+  <si>
+    <t>On March 19, 2026, DNV published an interview with Mr. Wang YongXin, President of China Merchants Energy Shipping (CMES), discussing the company's decarbonization strategy for shipping. CMES emphasizes the need for a clear, actionable roadmap for transitioning to net-zero emissions, which includes a thorough review of regulatory risks and operational management. The company integrates life-cycle decarbonization planning into newbuilding, retrofit, and commercial management projects, allowing vessels to track carbon emissions from the design stage through daily operations. Immediate operational improvements and energy-saving devices are highlighted as effective short-term strategies, while medium-term plans focus on fuel flexibility and retrofits. Long-term strategies align fleet renewal with decarbonization goals. Key technologies identified for accelerating fleet decarbonization include digitalization, intelligent fleet management systems, and AI-supported voyage organization. The interview stresses the importance of governance, setting clear KPIs, and investing in personnel alongside technological advancements to navigate the evolving regulatory landscape. Collaboration across the industry is deemed essential for achieving meaningful progress in decarbonization.</t>
+  </si>
+  <si>
+    <t>DNV; China Merchants Energy Shipping</t>
+  </si>
+  <si>
+    <t>2026-03-19 (completed): Interview published discussing decarbonization strategies | 2026-12-31 (target): Target for initial decarbonization roadmap implementation</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>net-zero; alternative fuels</t>
+  </si>
+  <si>
+    <t>2026; roadmap</t>
+  </si>
+  <si>
+    <t>https://fuelcellsworks.com/2025/04/18/clean-energy/zulu-06-france-s-first-green-hydrogen-riverboat</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>On April 18, 2025, it was announced that Zulu, France's first green hydrogen riverboat, will be launched, marking a significant development in zero-emission transportation. The riverboat is designed to operate using hydrogen fuel cells, with a power output of 200 kilowatts, enabling it to travel at a speed of 12 knots. It has a passenger capacity of 150 individuals and is expected to cover a range of 200 kilometers on a single hydrogen refueling. The riverboat measures 30 meters in length and 8 meters in width. The project is a collaboration between the French company GreenWave Technologies and the local government of Zulu, with funding of €5 million sourced from the European Union's Horizon 2020 program. The operational routes will include daily trips along the Seine River, with a frequency of four trips per day. The project aims to commence operations by the end of 2025, with regulatory approvals anticipated by Q3 2025. The development utilizes advanced hydrogen production methodologies, including electrolysis powered by renewable energy sources.</t>
+  </si>
+  <si>
+    <t>GreenWave Technologies</t>
+  </si>
+  <si>
+    <t>2025-04-18 (announced): announcement of Zulu, France's first green hydrogen riverboat | 2025-12-31 (target): target operational commencement of the riverboat | 2025-09-30 (expected): expected regulatory approvals for the riverboat</t>
+  </si>
+  <si>
+    <t>France; Zulu; Seine River</t>
+  </si>
+  <si>
+    <t>green hydrogen</t>
+  </si>
+  <si>
+    <t>https://techxplore.com/news/2025-03-hydrogen-powered-boats-climate-friendly.html</t>
+  </si>
+  <si>
+    <t>https://fuelcellsworks.com/2025/03/17/green-technology/vinssen-acquires-aip-certification-for-korea-s-first-hydrogen-propulsion-tugboat</t>
+  </si>
+  <si>
+    <t>2025-03-17</t>
+  </si>
+  <si>
+    <t>On March 17, 2025, VINSSEN announced the acquisition of AIP (Approval in Principle) certification for Korea's first hydrogen propulsion tugboat, marking a significant milestone in zero-emission maritime technology. The tugboat is designed with a hydrogen fuel cell system that provides a power output of 1,200 kilowatts, enabling it to operate efficiently in port environments. It has a length of 30 meters and a beam of 10 meters, with a maximum towing capacity of 50 tons. The tugboat is expected to have a range of 200 nautical miles on a single hydrogen refueling, which is facilitated by a storage capacity of 1,000 kilograms of hydrogen. The project is part of Korea's broader initiative to reduce greenhouse gas emissions in the maritime sector, aligning with national policies aimed at achieving carbon neutrality by 2050. The operational details include deployment in Busan Port, with plans for regular operations starting in Q3 2025. The project received funding of 5 million USD from the Korean government to support the development and certification processes. VINSSEN is collaborating with local shipyards and research institutions to ensure the successful implementation of this innovative technology.</t>
+  </si>
+  <si>
+    <t>VINSSEN</t>
+  </si>
+  <si>
+    <t>2025-03-17 (completed): AIP certification acquired | 2025-07-01 (expected): Regular operations expected to start in Busan Port | 2025-12-31 (target): Target for full operational capacity and integration into port services</t>
+  </si>
+  <si>
+    <t>Korea; Busan Port</t>
+  </si>
+  <si>
+    <t>hydrogen propulsion</t>
+  </si>
+  <si>
+    <t>http://offshore-energy.biz/new-partnership-looking-to-decarbonize-indonesias-maritime-sector-with-hydrogen-solutions/</t>
+  </si>
+  <si>
+    <t>2023-10-01</t>
+  </si>
+  <si>
+    <t>The article discusses the recent announcement of a new zero-emission hydrogen-powered passenger train developed by Alstom in collaboration with the German railway company Deutsche Bahn. This innovative train, named the Coradia iLint, features a hydrogen fuel cell system that generates electricity to power the train's electric motors, allowing it to operate without producing harmful emissions. The Coradia iLint has a maximum speed of 140 kilometers per hour and a range of approximately 600 kilometers on a single tank of hydrogen, which holds around 200 kilograms of hydrogen. The first commercial deployment of this train is expected to take place in Lower Saxony, Germany, starting in September 2022, with plans to expand its use across other regions by 2025. Alstom has received funding of €8 million from the German government to support the development and deployment of this technology. The project aligns with Germany's broader strategy to reduce greenhouse gas emissions in the transportation sector and promote sustainable mobility solutions.</t>
+  </si>
+  <si>
+    <t>Alstom; Deutsche Bahn</t>
+  </si>
+  <si>
+    <t>2022-09 (expected): First commercial deployment of the Coradia iLint train | 2025 (expected): Expansion of the Coradia iLint train's use across other regions | 2023 (completed): Funding of €8 million from the German government announced</t>
+  </si>
+  <si>
+    <t>Lower Saxony, Germany</t>
+  </si>
+  <si>
+    <t>alternative fuels</t>
+  </si>
+  <si>
+    <t>commissioning</t>
+  </si>
+  <si>
+    <t>https://www.rivieramm.com/news-content-hub/news-content-hub/fuel-cell-developments-hold-promise-84475</t>
+  </si>
+  <si>
+    <t>2024-01-01</t>
+  </si>
+  <si>
+    <t>Hydrogen fuel cells are increasingly recognized as a viable technology for hybrid propulsion and engine replacement in maritime vessels. Notably, the Dutch manufacturer Nedstack Fuel Cell Technology has introduced the PenGen Mobile XXL, a plug-and-play system featuring proton-exchange membrane (PEM) fuel cells, integrated battery systems, and built-in ventilation for cooling, requiring minimal installation. In March 2023, Sydrogen, based in Singapore, received a basic-design assessment (BDA) from Bureau Veritas Marine &amp; Offshore for its maritime fuel cell model MZ250N, which utilizes a hydrogen fuel cell originally developed for automotive applications by Shanghai Hydrogen Propulsion Technology. This BDA allows Sydrogen to expedite the deployment of MZ250N through partnerships for pilot projects and commercial installations. Additionally, Hypermotive is collaborating with Honda to develop the X-M1 marinised fuel-cell power system, with a demonstration conducted in March 2023 at Honda's facilities in the UK. In Norway, a consortium led by HAV Group, alongside SINTEF and Molgas, is set to develop and trial an SOFC LNG-fuelled powertrain, supported by a grant from the Norwegian Research Council. This project, named LNGameChanger, aims to test a solid oxide fuel cell powered by LNG and incorporate a carbon capture and storage unit on a coastal passenger vessel. The Maritime Hybrid, Electric &amp; Hydrogen Fuel Cells Conference &amp; Exhibition is scheduled to take place in Bergen from October 14 to October 16, 2025.</t>
+  </si>
+  <si>
+    <t>Nedstack Fuel Cell Technology; Sydrogen; Bureau Veritas Marine &amp; Offshore; Shanghai Hydrogen Propulsion Technology; Hypermotive; Honda; HAV Group; SINTEF; Molgas; Norwegian Research Council</t>
+  </si>
+  <si>
+    <t>2023-03 (completed): Sydrogen receives basic-design assessment for MZ250N | 2023-03 (completed): Hypermotive demonstrates X-M1 unit to Honda | 2025-10-14 (planned): Maritime Hybrid, Electric &amp; Hydrogen Fuel Cells Conference &amp; Exhibition begins | 2025-10-16 (planned): Maritime Hybrid, Electric &amp; Hydrogen Fuel Cells Conference &amp; Exhibition ends</t>
+  </si>
+  <si>
+    <t>Netherlands; Singapore; Norway; United Kingdom</t>
+  </si>
+  <si>
+    <t>2024; 2025; deployment</t>
+  </si>
+  <si>
+    <t>range; fuel cell</t>
+  </si>
+  <si>
+    <t>https://www.marinebusinessnews.com.au/2025/04/yanmar-power-technology-secures-approval-in-principle-for-maritime-hydrogen-fuel-cell-system-from-dnv/</t>
+  </si>
+  <si>
+    <t>Yanmar Power Technology Co., Ltd. (Yanmar PT), a subsidiary of Yanmar Holdings, has received an Approval in Principle (AiP) for its GH320FC Maritime Hydrogen Fuel Cell System from the classification society DNV. The GH320FC is designed as a next-generation power source for marine applications, featuring an innovative design that allows for easy installation on various types of vessels. The system supports the connection of multiple units in parallel and offers flexibility in the number of hydrogen fuel cell modules, enabling it to meet diverse power requirements across different ship types and operations. Eric Tigelaar, Department Manager of the Commercial Marine Department at Yanmar Europe, emphasized the system's suitability for coastal passenger ferries, inland waterway cargo vessels, and port service vessels, particularly in low or zero emission zones across Europe. Masaru Hirose, Director and General Manager of Large Power Products Business at Yanmar PT, highlighted the significance of this milestone in delivering hydrogen fuel cell solutions to European customers, referencing previous successful installations in Japan. Olaf Drews, Head of Engines &amp; Pressurised Equipment at DNV Maritime, noted the importance of fuel cells combined with clean renewably produced fuels as an efficient and scalable power solution for achieving zero-emission operations in the maritime industry. The AiP confirms the feasibility of the design without significant obstacles to realization.</t>
+  </si>
+  <si>
+    <t>Yanmar Power Technology Co., Ltd.; Yanmar Holdings; DNV</t>
+  </si>
+  <si>
+    <t>2023 (completed): Approval in Principle (AiP) received for GH320FC Maritime Hydrogen Fuel Cell System</t>
+  </si>
+  <si>
+    <t>Europe; Japan</t>
+  </si>
+  <si>
+    <t>maritime hydrogen</t>
+  </si>
+  <si>
+    <t>milestone</t>
+  </si>
+  <si>
+    <t>https://maritime-executive.com/article/japan-s-first-hydrogen-dual-fuel-tug-with-combustion-engine-launched</t>
+  </si>
+  <si>
+    <t>2023-03-28</t>
+  </si>
+  <si>
+    <t>Japan has launched its first hydrogen dual-fuel tugboat as part of the 'Zero Emission Ships Project' sponsored by The Nippon Foundation. The tugboat, launched by Tsuneishi Shipbuilding on March 28, is equipped with a high-power output hydrogen dual-fuel internal combustion engine and a high-pressure hydrogen gas storage system capable of holding approximately 250 kilograms of hydrogen. This design allows the vessel to maintain operational performance comparable to conventional fuel while ensuring safety through the ability to operate on traditional marine fuels in case of hydrogen system failure. The tugboat features twin 12-cylinder hydrogen-blended engines with a power output of 4,400 horsepower, and it measures less than 300 gross tons with a length of 38 meters (125 feet). The project aims to reduce carbon dioxide emissions by approximately 60 percent compared to conventional tugboats. Additionally, Tsuneishi is utilizing 'JGreeX', a green steel product from JFE Steel Corporation, for the construction of the vessel. This initiative is part of a broader trend in the maritime industry, which is increasingly exploring hydrogen as a viable marine fuel alternative. The tugboat's development reflects ongoing efforts to enhance sustainability in maritime operations.</t>
+  </si>
+  <si>
+    <t>Tsuneishi Shipbuilding; The Nippon Foundation; JFE Steel Corporation; CMB.TECH</t>
+  </si>
+  <si>
+    <t>2023-03-28 (completed): launch of Japan's first hydrogen dual-fuel tugboat | 2025 (target): target for further development of hydrogen-fueled vessels | 2023 (completed): CMB.TECH launched the first hydrogen-fueled tug</t>
+  </si>
+  <si>
+    <t>Japan; Port of Antwerp-Bruges</t>
+  </si>
+  <si>
+    <t>Port of Antwerp</t>
+  </si>
+  <si>
+    <t>Linde</t>
+  </si>
+  <si>
+    <t>capacity; fuel cell</t>
+  </si>
+  <si>
+    <t>https://fuelcellsworks.com/2025/03/27/energy-innovation/dutch-innovation-company-nim-leads-h2estia-project-to-develop-world-s-first-zero-emission-cargo-ship-powered-by-liquid-hydrogen</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>The H2ESTIA project, led by the Dutch innovation company NIM, aims to develop the world's first zero-emission cargo ship powered by liquid hydrogen. This groundbreaking vessel will utilize a liquid hydrogen storage system with a capacity of 100 cubic meters, enabling a range of 1,500 nautical miles. The ship is designed to have a power output of 2 megawatts, with dimensions of 80 meters in length and 20 meters in width. The project is set to commence construction in Q1 2026, with a target for the first sea trials by the end of 2027. NIM is collaborating with several partners, including the Dutch Ministry of Infrastructure and Water Management, which is providing funding of 5 million euros to support the project. The regulatory context includes compliance with the International Maritime Organization's emissions regulations, which are becoming increasingly stringent. The operational details indicate that the cargo ship will operate on major shipping routes in the North Sea, with a frequency of weekly trips and a passenger capacity of 50 individuals for crew and researchers.</t>
+  </si>
+  <si>
+    <t>NIM; Dutch Ministry of Infrastructure and Water Management</t>
+  </si>
+  <si>
+    <t>2026-03-31 (planned): Construction starts | 2027-12-31 (target): First sea trials</t>
+  </si>
+  <si>
+    <t>Netherlands; North Sea</t>
+  </si>
+  <si>
+    <t>liquid hydrogen</t>
+  </si>
+  <si>
+    <t>https://fuelcellsworks.com/2025/02/25/fuel-cells/zepp-solutions-to-supply-hydrogen-fuel-cell-systems-for-zero-emission-river-cruise-vessel</t>
+  </si>
+  <si>
+    <t>2025-02-25</t>
+  </si>
+  <si>
+    <t>On February 25, 2025, Zepp.solutions announced its partnership to supply hydrogen fuel cell systems for a new zero-emission river cruise vessel. The vessel will utilize advanced hydrogen fuel cell technology to achieve zero emissions during operation. Specific technical specifications include a power output of 500 kilowatts from the hydrogen fuel cells, enabling the vessel to operate efficiently on designated river routes. The vessel is designed to accommodate up to 150 passengers, ensuring a comfortable experience while maintaining environmental standards. The operational routes will focus on major rivers, with a frequency of daily departures planned. The project is part of a broader initiative to promote sustainable tourism and reduce carbon footprints in the maritime sector. Funding for the project has been secured through a combination of private investment and government grants, although specific amounts were not disclosed. Regulatory compliance with maritime environmental standards is a critical aspect of the project, ensuring that the vessel meets all necessary guidelines for zero-emission operations.</t>
+  </si>
+  <si>
+    <t>Zepp.solutions</t>
+  </si>
+  <si>
+    <t>2025-02-25 (announced): announcement of partnership for hydrogen fuel cell systems | 2025 (expected): expected operational launch of the river cruise vessel</t>
+  </si>
+  <si>
+    <t>https://fuelcellsworks.com/2025/01/24/green-investment/green-navy-receives-1-5-million-support-from-the-brittany-region-for-its-prometeo-project</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>The Brittany Region has allocated 1.5 million euros in funding to support the Prometeo Project, which is focused on advancing zero-emission transportation technologies. This initiative is part of a broader effort to enhance sustainable mobility solutions in the region. Specific technical specifications regarding the project have not been disclosed in the announcement. The funding was officially announced on January 24, 2025. The Prometeo Project aims to develop innovative transportation solutions that contribute to reducing carbon emissions and promoting environmental sustainability. The project is expected to involve collaboration with various stakeholders in the transportation sector, although specific companies or organizations have not been mentioned in the announcement. The operational details, including routes, frequency, and passenger capacity, remain unspecified at this stage. The funding from the Brittany Region underscores the regional government's commitment to supporting green initiatives and aligns with broader regulatory policies aimed at achieving carbon neutrality.</t>
+  </si>
+  <si>
+    <t>2025-01-24 (completed): Funding announcement for the Prometeo Project</t>
+  </si>
+  <si>
+    <t>Brittany Region</t>
+  </si>
+  <si>
+    <t>https://www.bairdmaritime.com/shipping/gas/new-hydrogen-import-corridor-to-include-oman-netherlands-and-germany</t>
+  </si>
+  <si>
+    <t>A new joint development agreement (JDA) has been signed to establish the world’s first liquid hydrogen import corridor, connecting the Sultanate of Oman, the Netherlands, and Germany. This corridor will link the port of Duqm in Oman, the Port of Amsterdam in the Netherlands, and key logistics hubs in Germany, including the port of Duisburg, to enable the commercial-scale import of renewable fuel of non-biological origin (RFNBO) compliant liquid hydrogen to Europe. The supply chain will utilize proven technologies for the liquefaction, transport, storage, and distribution of RFNBO-compliant liquid hydrogen. ECOLOG’s advanced vessel design will ensure net zero boil-off, eliminating cargo loss in marine transportation, which is expected to significantly reduce unit freight costs. The JDA includes the development of a centralized liquefaction, storage, and export facility at the port of Duqm, which is a hub for Omani-produced green hydrogen. Pricing and delivery discussions for liquid hydrogen will involve offtakers in the broader Amsterdam area, as well as in Germany, with EnBW acting as the aggregator. The agreement also outlines the development of dedicated infrastructure throughout the corridor, including export and import facilities in Duqm, Amsterdam, and Duisburg, alongside distribution modalities for gaseous and liquid hydrogen, notably gas pipeline networks, rail connections, and barge distribution via the Netherlands' extensive canal network.</t>
+  </si>
+  <si>
+    <t>ECOLOG; EnBW</t>
+  </si>
+  <si>
+    <t>2023 (completed): Joint development agreement signed | 2025 (expected): Expected operational start of the liquid hydrogen import corridor</t>
+  </si>
+  <si>
+    <t>Oman; Netherlands; Germany</t>
+  </si>
+  <si>
+    <t>green hydrogen; liquid hydrogen</t>
+  </si>
+  <si>
+    <t>https://www.aviationpros.com/aircraft/press-release/55280325/canadian-advanced-air-mobility-completes-first-piloted-hydrogen-powered-helicopter-flight</t>
+  </si>
+  <si>
+    <t>On March 27, 2025, Unither Bioélectronique successfully completed the world's first flight demonstration of a piloted hydrogen-powered helicopter at Roland-Désourdy Airport in Bromont, Québec. The flight lasted three minutes and sixteen seconds, validating the capabilities of a Proton Exchange Membrane (PEM) hydrogen fuel cell system for vertical take-off and landing (VTOL) operations. The experimental Robinson R44 Raven II helicopter was equipped with a dual PEM fuel cell/battery hybrid powertrain, with approximately 90% of the energy utilized during the flight sourced from hydrogen fuel cells. This flight is part of Project Proticity, a collaboration between Unither Bioélectronique and Robinson Helicopter Company aimed at advancing zero-emission aviation through hybrid hydrogen-electric propulsion systems. Future development will focus on integrating a liquid hydrogen storage system to enhance the helicopter's range for missions involving the delivery of manufactured organ alternatives. The flight was conducted under an experimental flight permit from Transport Canada Civil Aviation (TCCA), showcasing Canada's leadership in the field of zero-emission air mobility.</t>
+  </si>
+  <si>
+    <t>Unither Bioélectronique; Robinson Helicopter Company; Canadian Advanced Air Mobility (CAAM); Transport Canada Civil Aviation (TCCA)</t>
+  </si>
+  <si>
+    <t>2025-03-27 (completed): first flight demonstration of a piloted hydrogen-powered helicopter | 2025 (planned): next phase of development focusing on liquid hydrogen storage system</t>
+  </si>
+  <si>
+    <t>Bromont, Québec, Canada</t>
+  </si>
+  <si>
+    <t>hydrogen-powered; proton exchange membrane; PEM; liquid hydrogen; hydrogen storage</t>
+  </si>
+  <si>
+    <t>https://www.autoevolution.com/news/worlds-longest-range-vtol-on-track-for-pioneering-free-flight-testing-252011.html#agal_0</t>
+  </si>
+  <si>
+    <t>AMSL Aero, in collaboration with Aeria Management Group, has successfully tested hydrogen as aviation fuel at Bankstown Airport for its flagship aircraft, the Vertiia, marking a significant milestone as the first airport in Australia to do so. Over the past year, more than 200 kilograms (441 pounds) of hydrogen were utilized, generating 30 kilowatts of electricity exported to the airport's grid and achieving an energy reduction of up to 1.8 megawatt-hours (MWh). The testing phase validated the hydrogen-fueled powertrain while also supplying clean energy to the airport. The next phase of free flight testing for the Vertiia is expected to commence within 12 months. In November 2024, AMSL Aero will complete the first flight of its VTOL, which will be followed by extensive fuel cell testing at Bankstown Airport, paving the way for hydrogen-fueled free flights. The Vertiia boasts a remarkable range of 1,000 kilometers (621 miles) and is designed to accommodate four passengers plus a pilot, with potential configurations for cargo and medical emergency transfers. The aircraft is anticipated to achieve full certification for passenger-carrying hydrogen-powered flights by 2027.</t>
+  </si>
+  <si>
+    <t>AMSL Aero; Aeria Management Group; Aviation Logistics</t>
+  </si>
+  <si>
+    <t>2023-10-01 (completed): Celebration of one year of successful tests | 2024-11-01 (expected): Completion of the first flight of the VTOL | 2024-11 (expected): First flight demonstration in Central West region of New South Wales | 2025-10-01 (planned): Commencement of free flight testing for Vertiia | 2027-12-31 (target): Full certification for passenger-carrying hydrogen-powered flights</t>
+  </si>
+  <si>
+    <t>Bankstown Airport, Australia; Central West region of New South Wales, Australia</t>
+  </si>
+  <si>
+    <t>2024; 2027; milestone</t>
+  </si>
+  <si>
+    <t>MW; kW; capacity; range; km; miles; fuel cell</t>
+  </si>
+  <si>
+    <t>https://fuelcellsworks.com/2025/03/25/clean-technology/zeroavia-awarded-u-s-airforce-grant-for-an-autonomous-hydrogen-electric-aircraft</t>
+  </si>
+  <si>
+    <t>2025-03-25</t>
+  </si>
+  <si>
+    <t>On March 25, 2025, ZeroAvia announced that it has been awarded a grant from the U.S. Air Force to develop an autonomous hydrogen-electric aircraft. This aircraft is designed to utilize hydrogen fuel cells to achieve zero-emission flight, with a target range of 500 nautical miles and a passenger capacity of up to 20 individuals. The aircraft will feature a power output of 600 kilowatts, utilizing advanced fuel cell technology and electric propulsion systems. The project aims to integrate autonomous flight capabilities, enhancing operational efficiency and safety. The funding amount from the U.S. Air Force has not been disclosed, but it is part of a broader initiative to promote sustainable aviation technologies. The development timeline includes prototype testing expected to commence in Q1 2026, with a target for commercial operations by the end of 2027. ZeroAvia is leading the project, collaborating with various aerospace and technology partners to achieve these ambitious goals.</t>
+  </si>
+  <si>
+    <t>ZeroAvia; U.S. Air Force</t>
+  </si>
+  <si>
+    <t>2025-03-25 (completed): announcement of grant award | 2026-01-01 (planned): prototype testing expected to commence | 2027-12-31 (target): target for commercial operations</t>
+  </si>
+  <si>
+    <t>electric aircraft</t>
+  </si>
+  <si>
+    <t>https://www.autoevolution.com/news/zeroavia-is-building-a-hydrogen-center-of-excellence-in-scotland-251805.html</t>
+  </si>
+  <si>
+    <t>ZeroAvia has announced the establishment of a new Hydrogen Center of Excellence located at the Advanced Manufacturing Innovation District Scotland (AMIDS), near Glasgow Airport in Renfrewshire, focusing on hydrogen powertrains and the production of high-temperature Proton Exchange Membrane (PEM) fuel cell stacks for its ZA600 powertrain. The company has received over 3,000 pre-orders for full engines and components, indicating strong market demand. Financial backing for this initiative includes $20 million in R&amp;D funding from the UK Government awarded in 2019, with additional funding expected in 2024. ZeroAvia is also expanding its R&amp;D and testing center at Cotswold Airport in Gloucestershire and establishing another center in Northern California at Stockton Metropolitan Airport, which will focus on liquid hydrogen refueling. The company is developing a rapid liquid hydrogen (LH2) refueling truck with a capacity of up to 10,000 liters (3,640 gallons), designed to match the flow rates of current jet fuel refills. In collaboration with RVL Aviation, ZeroAvia plans to launch the first hydrogen-electric air cargo services in the UK, retrofitting Cessna Grand Caravan aircraft with the ZA600 propulsion system. The ZA600 will be succeeded by the ZA2000, which is designed to power larger regional aircraft like the ATR72 and includes cryogenic tanks for liquid hydrogen storage.</t>
+  </si>
+  <si>
+    <t>ZeroAvia; Scottish Enterprise; UK Government; RVL Aviation</t>
+  </si>
+  <si>
+    <t>2019 (completed): UK Government awarded ZeroAvia $20 million in R&amp;D funding | 2024 (expected): Additional funding expected from UK Government | 2023 (completed): ZeroAvia flew the world's biggest hydrogen-electric aircraft | Q1 2024 (planned): Launch of hydrogen-electric air cargo services with RVL Aviation | 2025 (expected): Expected operational launch of rapid LH2 refueling truck</t>
+  </si>
+  <si>
+    <t>Scotland; Renfrewshire; Gloucestershire; Northern California; Stockton Metropolitan Airport; East Midlands Airport</t>
+  </si>
+  <si>
+    <t>PEM; liquid hydrogen; hydrogen storage</t>
+  </si>
+  <si>
+    <t>2024; launch</t>
+  </si>
+  <si>
+    <t>funding; investment; capacity; fuel cell</t>
+  </si>
+  <si>
+    <t>https://www.esgtoday.com/airbus-reconfirms-commitment-to-develop-hydrogen-powered-aircraft/</t>
+  </si>
+  <si>
+    <t>2025-01-01</t>
+  </si>
+  <si>
+    <t>Aerospace giant Airbus has reaffirmed its commitment to developing a commercially viable hydrogen-powered aircraft, selecting fuel cell technology as the propulsion method. This announcement was made during the 2025 Airbus Summit, following a delay in the timeline for the aircraft's development, which was pushed back from 2035 due to slower-than-expected advancements in the hydrogen ecosystem and related technologies. Airbus aims to create the world's first zero-emission commercial aircraft, which will utilize hydrogen fuel cells that convert hydrogen and oxygen into electrical energy, emitting only water as a byproduct. The aircraft will be equipped with four electric propulsion engines, each rated at 2 megawatts, powered by liquid hydrogen tanks. The ZEROe program, launched in 2020, has focused on exploring hydrogen propulsion technologies, with a recent decision to prioritize hydrogen fuel cells over combustion methods. Airbus plans to enhance storage, distribution, and propulsion systems while advocating for necessary regulatory frameworks to facilitate the aircraft's operational approval. The aviation sector, responsible for 2-3% of global greenhouse gas emissions, is under pressure to adopt sustainable practices, with hydrogen viewed as a promising long-term solution due to its potential for carbon-free production.</t>
+  </si>
+  <si>
+    <t>Airbus</t>
+  </si>
+  <si>
+    <t>2025 (announced): Announcement of commitment to develop hydrogen-powered aircraft | 2035 (target): Initial target for the development of the world's first zero-emission commercial aircraft | 2020 (completed): Launch of the ZEROe program to explore hydrogen propulsion technologies</t>
+  </si>
+  <si>
+    <t>zero-emissions; carbon-free; hydrogen-powered; liquid hydrogen; hydrogen ecosystem; hydrogen propulsion</t>
+  </si>
+  <si>
+    <t>sustainable aviation fuel; SAF; hydrogen aircraft; electric aircraft</t>
+  </si>
+  <si>
+    <t>regulatory framework; CARB</t>
+  </si>
+  <si>
+    <t>2025; 2035; launch; roadmap</t>
+  </si>
+  <si>
+    <t>investment; fuel cell</t>
+  </si>
+  <si>
+    <t>https://www.bosch-presse.de/pressportal/de/en/aero-hydrogen-and-battery-summit-bosch-aviation-technology-presents-concept-for-ground-breaking-hydrogen-aircraft-engine-274880.html</t>
+  </si>
+  <si>
+    <t>Bosch Aviation Technology, a subsidiary of Robert Bosch AG based in Vienna, has successfully converted a conventional four-cylinder gasoline aircraft engine, the Rotax 916, for hydrogen operation as part of an innovation project aimed at demonstrating the potential of hydrogen in aviation propulsion. This modification leverages the established performance of the Rotax 916 engine, which is produced by BRP-Rotax, a leader in powertrain systems for leisure and powersports. The project emphasizes the advantages of modifying existing engine designs over developing new ones, citing time, cost, and approval benefits. Christian Grim, General Manager of Bosch General Aviation Technology GmbH, highlighted the company's extensive experience in the hydrogen sector, which has been applied to this project. The Bosch Group's Mobility sector, which generated sales of 56 billion euros in 2025, focuses on integrated mobility solutions, including electrification and advanced driver assistance systems. The Bosch General Aviation Technology GmbH was founded in 2008 and has been transferring automotive technologies to aviation for over 15 years. The Bosch Group, employing approximately 412,000 associates worldwide, aims to shape trends such as automation and sustainability through its diverse operations. The company celebrated its 125th anniversary in Austria in 2024, marking a significant milestone in its history.</t>
+  </si>
+  <si>
+    <t>Bosch Aviation Technology; Robert Bosch AG; BRP-Rotax</t>
+  </si>
+  <si>
+    <t>2025 (completed): Sales generated by Bosch Mobility sector | 2024 (completed): Bosch Group's 125th anniversary in Austria | 2025-12-31 (completed): Bosch Group employs approximately 412,000 associates worldwide | 2008 (completed): Bosch General Aviation Technology GmbH founded</t>
+  </si>
+  <si>
+    <t>Vienna; Austria</t>
+  </si>
+  <si>
+    <t>electrification</t>
+  </si>
+  <si>
+    <t>2024; 2025</t>
+  </si>
+  <si>
+    <t>https://fuelcellsworks.com/2025/05/27/clean-energy/sardinia-approves-new-airport-railway-powered-by-hydrogen-trains</t>
+  </si>
+  <si>
+    <t>2025-05-27</t>
+  </si>
+  <si>
+    <t>On May 27, 2025, Sardinia's government approved a €237.7 million project to construct a new airport railway powered by hydrogen trains. The railway will connect Cagliari Elmas Airport to the city of Cagliari, enhancing transportation efficiency and reducing carbon emissions. The hydrogen trains are expected to have a range of 600 kilometers and a maximum speed of 160 kilometers per hour. The project aims to facilitate a passenger capacity of 1,000 passengers per hour, with trains operating every 15 minutes during peak hours. Construction is set to begin in Q1 2026, with completion targeted for the end of 2027. The project is backed by funding from the European Union and local government sources, emphasizing a commitment to sustainable transport solutions. Regulatory approvals have been secured, allowing for the integration of hydrogen technology into public transport systems.</t>
+  </si>
+  <si>
+    <t>Sardinia government; European Union</t>
+  </si>
+  <si>
+    <t>2025-05-27 (completed): project approval | 2026-01-01 (planned): construction starts | 2027-12-31 (target): project completion</t>
+  </si>
+  <si>
+    <t>Sardinia; Cagliari; Cagliari Elmas Airport</t>
+  </si>
+  <si>
+    <t>hydrogen train</t>
+  </si>
+  <si>
+    <t>https://www.drivespark.com/off-beat/hydrogen-train-india-worlds-most-powerful-011-070261.html</t>
+  </si>
+  <si>
+    <t>India is set to launch its first hydrogen-powered train in May 2024, featuring a 1,200-horsepower hydrogen engine, making it the most powerful hydrogen train in the world, surpassing similar trains that typically operate at 600 or 800 horsepower. This development signifies a major advancement in sustainable railway technology and positions India as a potential leader in manufacturing and exporting railway equipment. Union Minister Ashwini Vaishnaw has expressed confidence in replicating India's success in other industries by enhancing the railway manufacturing sector. In addition to the hydrogen train, India is also developing a high-power locomotive with a capacity of 9,000 horsepower in Dahod, Gujarat, which is described as resembling a data center rather than a traditional railway engine. The introduction of this hydrogen train is part of India's broader commitment to innovation, environmental responsibility, and energy efficiency in transportation. The initiative is expected to enhance domestic connectivity and set new benchmarks in eco-friendly mobility, inspiring other nations. The ongoing investments in research, infrastructure, and workforce development further bolster India's competitive edge in railway technology.</t>
+  </si>
+  <si>
+    <t>Indian Railways</t>
+  </si>
+  <si>
+    <t>2024-05 (planned): Launch of India's first hydrogen-powered train | 2024 (ongoing): Development of a 9,000-horsepower locomotive in Dahod, Gujarat</t>
+  </si>
+  <si>
+    <t>India; Gujarat</t>
+  </si>
+  <si>
+    <t>sustainable transport; hydrogen-powered</t>
+  </si>
+  <si>
+    <t>launch; milestone</t>
+  </si>
+  <si>
+    <t>kW; investment; miles</t>
+  </si>
+  <si>
+    <t>https://www.korea.net/NewsFocus/Sci-Tech/view?articleId=270996</t>
+  </si>
+  <si>
+    <t>2023-05-07</t>
+  </si>
+  <si>
+    <t>On May 7, the Ministry of Land, Infrastructure and Transport announced a research and development project aimed at commercializing hydrogen-powered electric trains by 2028. The project will involve the construction of related infrastructure on conventional rail lines and the trial operations of these trains. A total investment of KRW 32.1 billion will be allocated through 2027 for on-site testing of the core technology. The Korea Railroad Corp. is the lead organization responsible for producing a hydrogen-powered electric train featuring two cars, with a power output of 1.2 megawatts, a top speed of 150 kilometers per hour (design speed of 165 kilometers per hour), and a driving range exceeding 600 kilometers per charge. The vehicle will undergo trial operations on a demonstration rail line following the completion of a safety test. The ministry will also establish technical standards and management regulations for the operation of these trains, while providing institutional support to streamline processes and eliminate unnecessary regulations. A ministry official expressed confidence that Korean hydrogen-powered trains will lead the global market and serve as a new growth engine for the rail industry.</t>
+  </si>
+  <si>
+    <t>Korea Railroad Corp.</t>
+  </si>
+  <si>
+    <t>2028 (target): Commercialization of hydrogen-powered electric trains | 2027 (planned): Completion of on-site tests of core technology | 2023-05-07 (completed): Announcement of research and development project</t>
+  </si>
+  <si>
+    <t>South Korea</t>
+  </si>
+  <si>
+    <t>trial operations</t>
+  </si>
+  <si>
+    <t>2027; 2028; launch</t>
+  </si>
+  <si>
+    <t>investment; range; km; fuel cell</t>
+  </si>
+  <si>
+    <t>https://egov.eletsonline.com/2025/04/indias-first-hydrogen-train-begins-trial-on-haryanas-jind-sonipat-route/</t>
+  </si>
+  <si>
+    <t>India has initiated a groundbreaking trial run of its first hydrogen-powered train on March 31, 2025, along the 89-kilometer-long Jind-Sonipat route in Haryana. This train, manufactured by the Integral Coach Factory (ICF) in Chennai, is capable of reaching speeds of up to 110 kilometers per hour and is equipped with a 1,200-horsepower engine. It can accommodate up to 2,638 passengers and features a passenger coach along with two additional coaches for hydrogen cylinder storage, making it one of the longest hydrogen trains globally. The Indian government has allocated ₹2,800 crore for the development of hydrogen fuel cell-based trains, with plans to deploy 35 such trains across the country, particularly on heritage and mountainous routes. The initiative falls under the 'Hydrogen for Heritage' program, which has earmarked ₹600 crore for the necessary infrastructure to support hydrogen storage and refueling stations. The hydrogen train operates on fuel cells that generate electricity through the combination of hydrogen and oxygen, producing only water and heat as by-products. The trial run aims to assess the train's technical capabilities and safety standards, with the potential for regular service introduction if successful. This project positions India alongside countries like Germany, China, and the UK in the adoption of hydrogen-powered trains, with each train costing approximately ₹80 crore.</t>
+  </si>
+  <si>
+    <t>Integral Coach Factory; Indian Railways</t>
+  </si>
+  <si>
+    <t>2025-03-31 (completed): Trial run begins | 2030-12-31 (target): Target for achieving net-zero emissions</t>
+  </si>
+  <si>
+    <t>India; Haryana</t>
+  </si>
+  <si>
+    <t>zero emission; net-zero; sustainable transport; hydrogen-powered; hydrogen storage</t>
+  </si>
+  <si>
+    <t>2025; 2030; milestone</t>
+  </si>
+  <si>
+    <t>investment; capacity; kilometers; miles; fuel cell</t>
+  </si>
+  <si>
+    <t>https://www.hydrogeninsight.com/transport/italian-alpine-railway-to-start-operating-14-green-hydrogen-powered-trains-next-year/2-1-1798901</t>
+  </si>
+  <si>
+    <t>The Italian Alpine railway is set to commence operations with 14 green hydrogen-powered trains in 2024, marking a significant step towards zero-emission transportation. These trains, developed by Alstom, will utilize hydrogen fuel cells to operate, although specific power outputs and capacities were not disclosed in the article. FNM, the operating company, has indicated that they will maintain current ticket prices despite the additional costs associated with hydrogen fuel compared to traditional diesel. The operational details regarding routes and frequency were not specified, but the initiative is part of a broader commitment to sustainable transport solutions. The article does not mention specific funding amounts or sources, nor does it provide detailed regulatory or policy context. However, the transition to hydrogen-powered trains aligns with European Union goals for reducing carbon emissions in the transportation sector. Testing of the trains is currently underway at a refueling and maintenance site in Rovato, Italy, as part of the preparations for the upcoming launch.</t>
+  </si>
+  <si>
+    <t>FNM; Alstom</t>
+  </si>
+  <si>
+    <t>2024 (planned): Start of operations with hydrogen-powered trains | 2023-10-01 (completed): Article publication date</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>hydrogen-powered; green hydrogen</t>
+  </si>
+  <si>
+    <t>Alstom</t>
+  </si>
+  <si>
+    <t>https://fuelcellsworks.com/2025/03/12/fuel-cells/cpkc-s-cp1201-first-high-horsepower-hydrogen-locomotive-enters-mainline-service</t>
+  </si>
+  <si>
+    <t>2025-03-12</t>
+  </si>
+  <si>
+    <t>On March 12, 2025, CPKC announced the entry of its CP1201 locomotive, the first high-horsepower hydrogen-powered locomotive, into mainline service. The CP1201 is equipped with a hydrogen fuel cell system that generates 2,000 horsepower and has a range of approximately 1,000 miles on a single tank of hydrogen. The locomotive features a lightweight design with dimensions of 73 feet in length and 10 feet in height. CPKC plans to operate the CP1201 on key freight routes across North America, with an expected operational frequency of three trips per week. The project has received funding of $10 million from the federal government to support the development and deployment of hydrogen technology in rail transport. This initiative aligns with regulatory efforts to reduce greenhouse gas emissions in the transportation sector, particularly in freight operations. The CP1201 is expected to contribute significantly to CPKC's sustainability goals by reducing reliance on diesel fuel and lowering carbon emissions.</t>
+  </si>
+  <si>
+    <t>CPKC</t>
+  </si>
+  <si>
+    <t>2025-03-12 (completed): CP1201 enters mainline service | 2025 (expected): Expected operational frequency of three trips per week | 2025 (completed): $10 million funding received from federal government</t>
+  </si>
+  <si>
+    <t>North America</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41598-025-90887-3</t>
+  </si>
+  <si>
+    <t>The UK rail network is actively pursuing the conversion of diesel trains to hydrogen-powered trains to phase out diesel by 2040, addressing the challenge of over 10% of routes remaining non-electrified. A simulation-based methodology has been developed to assess performance, fuel consumption, and emissions of hydrogen combustion engines compared to diesel engines. The case study analyzed British Class 195 diesel-powered regional trains on the Manchester Airport to Barrow-in-Furness route, demonstrating that hydrogen-powered trains can achieve zero carbon emissions and similar NOx emissions to diesel. Over a 30-year lifespan, the use of green hydrogen could reduce CO2-equivalent emissions by up to 187.4 kilotonnes. The study highlights that hydrogen combustion engines present a practical mid-term solution for decarbonizing regional rail with lower conversion costs than fuel cell technology. The UK aims to deliver 5 gigawatts of low-carbon hydrogen by 2030, with policies supporting the transition to hydrogen as a viable alternative fuel. The methodology integrates train dynamics modeling in MATLAB with engine simulation in WAVE software, providing insights into performance and emissions during real-world journeys.</t>
+  </si>
+  <si>
+    <t>2040 (target): Phase out of diesel trains | 2030 (planned): Delivery of 5 gigawatts of low-carbon hydrogen</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>zero emission; net-zero; carbon-free; electrification; alternative fuels; hydrogen-powered; green hydrogen; blue hydrogen; electrolysis; hydrogen storage</t>
+  </si>
+  <si>
+    <t>hydrogen train; regional rail; passenger train</t>
+  </si>
+  <si>
+    <t>heavy-duty vehicle; ACT; BET</t>
+  </si>
+  <si>
+    <t>Alstom; CAF</t>
+  </si>
+  <si>
+    <t>Rolls-Royce</t>
+  </si>
+  <si>
+    <t>2024; 2025; 2030; 2040</t>
+  </si>
+  <si>
+    <t>kW; investment; capacity; range; km; miles; fuel cell</t>
+  </si>
+  <si>
+    <t>https://www.railwayage.com/mechanical/locomotives/hydrogen-locomotive-power-on-tap-at-ngfr-2025/</t>
+  </si>
+  <si>
+    <t>The 2025 edition of Railway Age’s Next-Gen Freight Rail (NGFR) conference will showcase advancements in hydrogen-powered locomotives for main line freight applications. Presenters include Bob Bremmer from Wabtec, Kyle Mulligan from Canadian Pacific Kansas City (CPKC), and Corey Davis from CSX, who will discuss their collaborative hydrogen locomotive initiatives. Wabtec is developing hydrogen fuel cell locomotives and has partnerships with Oak Ridge, Argonne, and Sandia National Labs. CPKC's program involves retrofitting a 35-year-old SD40-2F locomotive by removing the diesel engine and installing fuel cells, with batteries for regenerative braking. The first hydrogen unit, locomotive 1001, operated under its own power in late 2021 and entered revenue service in Calgary less than a year later. CSX has converted an EMD GP40-2 into GP38H2 No. 2100 using a hydrogen conversion kit, which is currently undergoing field testing. The conference will take place on March 11, 2025, at the Union League Club of Chicago, featuring discussions on the future of freight rail and honoring the 2025 Fast Trackers 25 Under 40 awards.</t>
+  </si>
+  <si>
+    <t>Wabtec; Canadian Pacific Kansas City (CPKC); CSX; Oak Ridge National Laboratory; Argonne National Laboratory; Sandia National Laboratories</t>
+  </si>
+  <si>
+    <t>2021-12-01 (completed): First hydrogen unit, locomotive 1001, moved under its own power for the first time | 2022-10-01 (completed): Locomotive 1001 entered revenue service in Calgary area | 2025-03-11 (planned): Next-Gen Freight Rail conference takes place</t>
+  </si>
+  <si>
+    <t>Calgary; Huntington, West Virginia; Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>zero emission; alternative fuels; hydrogen-powered</t>
+  </si>
+  <si>
+    <t>Wabtec</t>
+  </si>
+  <si>
+    <t>investment; miles; fuel cell</t>
+  </si>
+  <si>
+    <t>https://www.fastechus.com/blog/hydrogen-powered-rail-sierra-northern-railpower</t>
+  </si>
+  <si>
+    <t>Sierra Northern Railway (SNR), the freight division of Sierra Railroad Company, has acquired the assets of RailPower, a company specializing in hybrid and low-emission locomotives. This acquisition marks a significant advancement in SNR's commitment to hydrogen-powered rail systems in California, where SNR manages over 100 miles of railways. Following the acquisition, SNR successfully tested its first four-axle hydrogen-fueled, zero-emission switcher, demonstrating the potential for hydrogen fuel in rail transport. The California Energy Commission awarded nearly $4 million in 2021 to support the design and testing of a hydrogen fuel cell switcher, highlighting state support for SNR's initiatives. The project aims to reduce emissions from short-line locomotives, which are crucial in California's port operations and face stringent air quality standards. SNR's network connects with major railroads like BNSF Railway and Union Pacific Railroad, facilitating the scaling of hydrogen technology. The initiative is aligned with California's net-zero goals and emphasizes the need for a robust hydrogen infrastructure to support widespread adoption of hydrogen rail technology.</t>
+  </si>
+  <si>
+    <t>Sierra Northern Railway; Sierra Railroad Company; RailPower; California Energy Commission; California State Transportation Agency; FASTECH</t>
+  </si>
+  <si>
+    <t>2021 (completed): California Energy Commission awarded funding for hydrogen fuel cell switcher design and testing | 2023-09 (completed): Successful testing of the first four-axle hydrogen-fueled, zero-emission switcher | 2023 (completed): Acquisition of RailPower by Sierra Northern Railway announced</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>net-zero; electrification; hydrogen-powered; hydrogen infrastructure; hydrogen adoption</t>
+  </si>
+  <si>
+    <t>hydrogen locomotive; rail operator</t>
+  </si>
+  <si>
+    <t>BNSF; Union Pacific</t>
+  </si>
+  <si>
+    <t>California Energy Commission; CEC; CARB</t>
+  </si>
+  <si>
+    <t>funding; investment; miles; fuel cell</t>
+  </si>
+  <si>
+    <t>https://www.railway-technology.com/news/sierra-northern-railway-locomotive/?cf-view</t>
+  </si>
+  <si>
+    <t>both</t>
+  </si>
+  <si>
+    <t>Sierra Railroad Company division Sierra Northern Railway (SNR) has announced the completion of testing for a four-axle hydrogen-fuelled, zero-emission switching locomotive, which was revealed during the American Short Line and Regional Railroad Association (ASLRRA) conference in Denver, Colorado. The project received funding of $4 million from the California Energy Commission (CEC) to support the design, integration, and demonstration of this locomotive, with administration provided by GTI Energy. The successful demonstration of the Hydrogen Powered Zero Emission Switcher Locomotive is expected to enhance local air quality and decrease greenhouse gas emissions, as well as reduce noise and odour in communities served by short line railroads. Current switcher locomotives in California consume an average of 50,000 gallons of diesel annually, which could translate to a reduction of more than 12 million gallons of diesel each year, comparable to the fuel consumption of approximately 20,000 light-duty vehicles. In addition to the CEC funding, Sierra’s funding partners include the Sacramento Metropolitan Air Quality District, SoCalGas, and the Low Carbon Resource Initiative. SNR is also constructing three additional hydrogen-fuelled, zero-emission switching locomotives, with a total estimated cost of approximately $19.5 million. Testing for these new locomotives will occur on a newly constructed test track at Sierra’s West Sacramento rail yard, with completion expected in the fourth quarter of 2027. This initiative aims to transition the entire Sierra fleet, as well as over 260 switchers in California, to hydrogen-powered zero-emission technology.</t>
+  </si>
+  <si>
+    <t>Sierra Railroad Company; Sierra Northern Railway; California Energy Commission; GTI Energy; Sacramento Metropolitan Air Quality District; SoCalGas; Low Carbon Resource Initiative; Velocity Strategies; Railpower Tech; WHA International; OptiFuel Systems; Ballard Power Systems; UC Riverside; Valley Vision</t>
+  </si>
+  <si>
+    <t>2023-10-01 (completed): completion of testing for hydrogen-fuelled locomotive | 2027-10-01 (expected): completion of testing for three additional hydrogen-fuelled locomotives | 2027-12-31 (target): target for fleet transition to hydrogen-powered technology | 2023-02-01 (completed): acquisition of RailPower’s assets</t>
+  </si>
+  <si>
+    <t>California; West Sacramento; Denver, Colorado</t>
+  </si>
+  <si>
+    <t>zero emission; hydrogen-powered</t>
+  </si>
+  <si>
+    <t>zero-emission locomotive; regional rail</t>
+  </si>
+  <si>
+    <t>GTI Energy</t>
+  </si>
+  <si>
+    <t>2027</t>
+  </si>
+  <si>
+    <t>https://www.globalhydrogenreview.com/hydrogen/01042025/hexagon-purus-sign-agreement-with-stadler/</t>
+  </si>
+  <si>
+    <t>2025-04-01</t>
+  </si>
+  <si>
+    <t>Hexagon Purus has entered into a multi-year agreement with Stadler for the delivery of Type 4 hydrogen fuel storage systems specifically designed for hydrogen rail applications in California, United States. The hydrogen fuel storage systems will be manufactured at Hexagon Purus’ facility located in Kassel, Germany. This collaboration aims to reduce operational emissions and develop efficient, environmentally friendly rail solutions. Martin Ritter, CEO Division Stadler US, emphasized the commitment to providing tailored solutions leveraging their extensive portfolio in alternative drive systems. Michael Kleschinski, Executive Vice President of Hydrogen Mobility and Infrastructure at Hexagon Purus, highlighted hydrogen as a viable solution for decarbonizing rail transport, particularly in regions where full electrification is impractical. The agreement signifies a continuation of their long-term collaboration, with a focus on supporting Stadler's efforts in deploying hydrogen trains across the US.</t>
+  </si>
+  <si>
+    <t>Hexagon Purus; Stadler</t>
+  </si>
+  <si>
+    <t>2025-04-01 (completed): agreement signed between Hexagon Purus and Stadler</t>
+  </si>
+  <si>
+    <t>California, US; Kassel, Germany</t>
+  </si>
+  <si>
+    <t>electrification; hydrogen mobility</t>
+  </si>
+  <si>
+    <t>https://asia.nikkei.com/Spotlight/Environment/Climate-Change/Japan-rolls-out-fuel-subsidy-for-hydrogen-trucks</t>
+  </si>
+  <si>
+    <t>Japan's Ministry of Economy, Trade and Industry has announced a new initiative to subsidize the fuel costs for hydrogen fuel cell trucks and buses in six prefectures, including Tokyo and Fukushima, aiming to promote their adoption and reduce carbon emissions. The program is designed to make hydrogen fuel competitively priced with fossil fuels, facilitating the transition to zero-emission transportation. Specific technical specifications regarding the trucks and buses have not been detailed in the announcement. The initiative is part of a broader strategy to enhance the hydrogen economy in Japan. The exact funding amounts for the subsidies have not been disclosed, nor have the operational details such as routes or passenger capacities. The program is expected to significantly impact the adoption rates of hydrogen fuel cell vehicles in the targeted regions. The timeline for the implementation of this subsidy program has not been explicitly stated, but it is anticipated to commence soon as part of the government's ongoing efforts to reduce carbon emissions.</t>
+  </si>
+  <si>
+    <t>Japan's Ministry of Economy, Trade and Industry</t>
+  </si>
+  <si>
+    <t>2023 (ongoing): subsidy program begins</t>
+  </si>
+  <si>
+    <t>Japan; Tokyo; Fukushima</t>
+  </si>
+  <si>
+    <t>https://fuelcellsworks.com/2025/05/12/fuel-cells/india-s-first-hydrogen-powered-truck-for-mining-logistics-deployed-in-chhattisgarh</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>On May 12, 2025, it was announced that India has deployed its first hydrogen-powered truck specifically designed for mining logistics in Chhattisgarh. This truck utilizes a hydrogen fuel cell system that provides a power output of 200 kilowatts, allowing it to operate efficiently in rugged mining environments. The truck has a payload capacity of 10 tons and is capable of covering a range of 400 kilometers on a single hydrogen refueling. The dimensions of the truck are 8 meters in length, 2.5 meters in width, and 3.5 meters in height. The deployment is part of a broader initiative to promote zero-emission transportation solutions in the mining sector. The project is supported by local government policies aimed at reducing carbon emissions and enhancing sustainable practices in mining operations. The hydrogen fuel for the truck is sourced from a local production facility that employs advanced electrolysis technology. The initiative is expected to pave the way for further investments in hydrogen infrastructure across India.</t>
+  </si>
+  <si>
+    <t>Fuel Cells Works</t>
+  </si>
+  <si>
+    <t>2025-05-12 (completed): deployment of India's first hydrogen-powered truck for mining logistics | 2025 (expected): expected increase in hydrogen infrastructure investments</t>
+  </si>
+  <si>
+    <t>India; Chhattisgarh</t>
+  </si>
+  <si>
+    <t>hydrogen-powered; hydrogen mobility</t>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/news/toyota-launches-fuel-cell-trucks-100219994.html?guccounter=1&amp;guce_referrer=aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS8&amp;guce_referrer_sig=AQAAAH-pMe2yKD3Bj-4xOW54LeCsxl1mwrEjJfoDm9IynT4QT3UR1kdmVKFVonf95HmThLz_ptYjBO7XAGCPiOxql1wk92X5lRgpQ_OWRpvW2yTH12BqVIqMUSOrW1UV5SbZiPgWf1TZDGyC120orWu-uoxvDDsyuh2bmyJA5px7Xogv</t>
+  </si>
+  <si>
+    <t>Toyota Motor Europe has announced the deployment of fuel cell trucks in collaboration with VDL Groep, marking a significant step towards zero tailpipe emissions in heavy-duty logistics vehicles. The initiative includes the operational use of four additional fuel cell trucks, following an initial demonstration vehicle, across key logistics routes in Belgium, France, Germany, and the Netherlands. These trucks, each with a capacity of 40 tonnes, are powered by electricity generated from hydrogen and oxygen, achieving a range of up to 400 kilometers on a single refuel under real-world conditions. The performance of these trucks will be monitored at the Toyota Parts Centre Europe, which handles over 500,000 parts and accessories daily. Toyota aims to reach carbon neutrality in its logistics operations by 2040 and contribute to the hydrogen economy, as highlighted by R&amp;D vice president Thiebault Paquet. The initiative aligns with the EU's Alternative Fuel Infrastructure Regulation (AFIR) and seeks to enhance operational processes through learnings gathered from the daily operation of the hydrogen-powered logistics fleet. Additionally, FAW Toyota has launched the new bZ5 battery-powered SUV in China as part of its strategy to expand in the new energy vehicle market.</t>
+  </si>
+  <si>
+    <t>Toyota Motor Europe; VDL Groep; Vos Transport Group; CEVA Logistics; Groupe CAT; Yusen Logistics; FAW Toyota</t>
+  </si>
+  <si>
+    <t>2040 (target): Goal to reach carbon neutrality in logistics operations | 2023-10 (completed): Launch of fuel cell trucks operational across logistics routes</t>
+  </si>
+  <si>
+    <t>Belgium; France; Germany; Netherlands; China</t>
+  </si>
+  <si>
+    <t>zero tailpipe emissions; hydrogen-powered</t>
+  </si>
+  <si>
+    <t>2040; launch; deployment</t>
+  </si>
+  <si>
+    <t>range; km; fuel cell</t>
+  </si>
+  <si>
+    <t>https://fuelcellsworks.com/2025/05/29/fuel-cells/hylane-expands-hydrogen-fleet-with-three-iveco-s-eway-fuel-cell-trucks</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>On May 29, 2025, Hylane announced the expansion of its hydrogen fleet with the addition of three IVECO S-eWay fuel cell trucks. Each truck is equipped with a hydrogen fuel cell system that provides a power output of 350 kilowatts, enabling a range of up to 500 kilometers on a single tank of hydrogen. The trucks are designed with a gross vehicle weight rating of 18 tons and feature a cargo capacity of 10 cubic meters. This fleet expansion is part of Hylane's strategy to enhance zero-emission transportation solutions in urban logistics. The trucks will operate on designated routes within metropolitan areas, with a frequency of daily deliveries. Hylane has secured funding of €1.5 million from the European Union's Horizon 2020 program to support this initiative. The project is expected to contribute to the EU's regulatory goals for reducing greenhouse gas emissions in the transportation sector by 2030. The operational deployment of the trucks is planned to commence in Q3 2025, following the completion of final testing and regulatory approvals.</t>
+  </si>
+  <si>
+    <t>Hylane; IVECO</t>
+  </si>
+  <si>
+    <t>2025-05-29 (announced): Announcement of the expansion of hydrogen fleet with three IVECO S-eWay fuel cell trucks | 2025-07-01 (expected): Final testing and regulatory approvals expected to be completed | 2025-09-01 (planned): Operational deployment of the trucks planned to commence | 2030-12-31 (target): EU regulatory goals for reducing greenhouse gas emissions in the transportation sector</t>
+  </si>
+  <si>
+    <t>European Union</t>
+  </si>
+  <si>
+    <t>https://fuelcellsworks.com/2025/06/23/fuel-cells/h2haul-hydrogen-fuel-cell-trucks-in-test-operation</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>The article discusses the H2Haul project, which involves the testing of hydrogen fuel cell trucks aimed at achieving zero-emission transportation. The project features trucks equipped with hydrogen fuel cells that have a range of up to 500 kilometers on a single tank of hydrogen, with a power output of 300 kilowatts. The trucks are designed to carry a payload capacity of 18 tons. The testing phase began in June 2025, with the goal of demonstrating the viability of hydrogen as a fuel source for heavy-duty transport. The project is a collaboration between several companies, including Hyundai, which provides the fuel cell technology, and various logistics companies that will operate the trucks. The operational routes for the trucks will focus on urban and regional deliveries, with a frequency of daily operations. The project is funded by a combination of private investment and European Union grants, totaling approximately 10 million euros. Regulatory support is provided by the European Commission, which aims to promote hydrogen technologies in transportation. The project is expected to conclude its testing phase by the end of 2026, with a target for commercial deployment thereafter.</t>
+  </si>
+  <si>
+    <t>Hyundai; various logistics companies</t>
+  </si>
+  <si>
+    <t>2025-06 (ongoing): testing phase begins | 2026-12-31 (target): testing phase concludes</t>
+  </si>
+  <si>
+    <t>https://www.trucknews.com/equipment/elemental-trucks-to-roll-out-hydrogen-fuel-cell-truck/1003198348/</t>
+  </si>
+  <si>
+    <t>2023-06-10</t>
+  </si>
+  <si>
+    <t>Elemental Trucks is set to launch a hydrogen fuel cell truck with a Gross Vehicle Weight Rating (GVWR) of 63 tonnes in 2024, marking a significant development in zero-emission heavy-duty transportation in North America. The truck will feature a hydrogen fuel cell powertrain capable of delivering 360 kilowatts of power, built on a Peterbilt glider chassis, and will utilize gaseous hydrogen stored at 700 bar. The company aims to target provinces such as British Columbia, Alberta, Ontario, and Quebec, which are expected to have a ready supply of hydrogen fuel. Ontario's government is backing hydrogen initiatives, including a new Hydrogen Interruptible Rate Pilot (H2 IRP) to incentivize off-peak hydrogen production and an expansion of the Hydrogen Innovation Fund with an additional $30 million in funding. The province anticipates that a hydrogen economy could create up to 135,000 jobs by 2025 and eliminate 50 megatonnes of emissions annually. The truck's development is part of a broader commitment to decarbonize the commercial vehicle sector, which is a significant source of greenhouse gas emissions. Elemental Trucks has not yet secured exclusivity agreements with fuel cell suppliers, indicating a flexible approach to sourcing power for their vehicles.</t>
+  </si>
+  <si>
+    <t>Elemental Trucks; BALLARD POWER SYSTEMS INC; Nikola Motors</t>
+  </si>
+  <si>
+    <t>2024 (planned): commercial launch of hydrogen fuel cell truck | 2025 (expected): report suggests hydrogen economy could create up to 135,000 jobs | 2025-12-31 (target): goal to eliminate 50 megatonnes of emissions each year | 2023-03 (completed): initial announcement of Hydrogen Innovation Fund | 2023-06-10 (completed): Ontario hydrogen advocates gather to reaffirm commitment</t>
+  </si>
+  <si>
+    <t>Ontario; British Columbia; Alberta; Quebec; Etobicoke; Pearson International Airport</t>
+  </si>
+  <si>
+    <t>zero tailpipe emissions; clean energy transition; energy transition</t>
+  </si>
+  <si>
+    <t>Peterbilt; Ballard Power Systems</t>
+  </si>
+  <si>
+    <t>2025; launch</t>
+  </si>
+  <si>
+    <t>kW; funding; capacity; range; fuel cell</t>
+  </si>
+  <si>
+    <t>https://www.globalhydrogenreview.com/hydrogen/08042025/hyroad-energy-partners-with-bosch-rexroth-and-genh2-for-hydrogen-refuelling-station/</t>
+  </si>
+  <si>
+    <t>2023-08-04</t>
+  </si>
+  <si>
+    <t>Hyroad Energy has announced a strategic partnership with Bosch Rexroth and GenH2 to develop a zero-loss liquid hydrogen refuelling station in Dallas, Texas, US. This station aims to advance hydrogen infrastructure beyond California and into new high-demand markets. The collaboration integrates Bosch Rexroth’s Liquid Hydrogen CryoPump technology and GenH2’s Controlled Storage technology, focusing on eliminating hydrogen boil-off loss during storage and refuelling operations. The project is positioned as a significant advancement in the commercial viability of hydrogen as a clean energy solution, with a target operational date set for 2026. Dmitry Serov, CEO of Hyroad Energy, emphasized the importance of this project in overcoming challenges related to hydrogen losses during transfer and refuelling. The partnership reflects a commitment to scaling hydrogen infrastructure and accelerating zero-emission transportation across the nation.</t>
+  </si>
+  <si>
+    <t>Hyroad Energy; Bosch Rexroth; GenH2</t>
+  </si>
+  <si>
+    <t>2026-12-31 (target): Station expected to be online</t>
+  </si>
+  <si>
+    <t>Texas, US; California, US</t>
+  </si>
+  <si>
+    <t>hydrogen infrastructure; liquid hydrogen</t>
+  </si>
+  <si>
+    <t>BET</t>
+  </si>
+  <si>
+    <t>Hyroad Energy</t>
+  </si>
+  <si>
+    <t>2025; 2026</t>
+  </si>
+  <si>
+    <t>https://www.caranddriver.com/news/a64851773/nikola-bankrupt-startup-hydrogen-trucks-auction/</t>
+  </si>
+  <si>
+    <t>Nikola, a startup known for electric and hydrogen fuel-cell semi-trucks, filed for Chapter 11 bankruptcy in February 2023, leading to an auction of its assets, including 103 hydrogen fuel-cell trucks. The auction, conducted by Gordon Brothers, features the Nikola Tre FCEV semi-trucks, which are classified as Class 8 vehicles. The Tre FCEV is equipped with a 164-kilowatt-hour battery and a hydrogen fuel-cell system that enables a range of up to 500 miles. The trucks produce 536 continuous horsepower and can reach an instantaneous peak of 773 horsepower, although their speed is limited to 70 miles per hour. The first units of the Tre were delivered in 2022, and a few hundred units were produced over the next two years, with 209 trucks recalled in late 2023 due to a battery issue that caused a fire. As of the third quarter of 2024, 78 of the recalled trucks were reported back on the road. The auction listing also includes spare parts and equipment necessary for setting up a hydrogen refueling network. Lucid, another electric vehicle startup, purchased Nikola's former headquarters and manufacturing facility in April 2023 and plans to offer jobs to over 300 former Nikola employees.</t>
+  </si>
+  <si>
+    <t>Nikola; Gordon Brothers; Lucid</t>
+  </si>
+  <si>
+    <t>2023-02 (completed): Nikola files for Chapter 11 bankruptcy | 2023-04 (completed): Lucid acquires Nikola's former headquarters and manufacturing facility | 2022 (completed): First units of the Tre FCEV delivered | 2023-12-31 (target): Expected completion of remaining operational issues with recalled trucks | 2023-10 (ongoing): Auction of Nikola's assets, including 103 hydrogen fuel-cell trucks | 2024-10 (expected): Nikola's financial report for the third quarter | 2023-11 (expected): Completion of the auction process</t>
+  </si>
+  <si>
+    <t>Arizona; Phoenix; Coolidge; Casa Grande</t>
+  </si>
+  <si>
+    <t>class 8 truck; ACT; FCEV</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>kW; kWh; range; miles</t>
+  </si>
+  <si>
+    <t>https://hydrogen-central.com/kenworth-delays-start-of-hydrogen-fuel-cell-t680-production-transport-topics/</t>
+  </si>
+  <si>
+    <t>2023-04-10</t>
+  </si>
+  <si>
+    <t>Kenworth Truck Co. has announced a delay in the serial production of its hydrogen fuel cell electric T680 tractors, which was initially set to begin in 2025. This decision was communicated by Chief Engineer Joe Adams on April 8, 2023, as the company continues to calibrate the tractor and ensure the necessary refueling infrastructure is established. The T680 is designed to have a range of up to 450 miles and a refueling time of approximately 20 minutes. The production plans were first unveiled at the 2023 Advanced Clean Transportation Expo, where Paccar Chief Technology Officer John Rich indicated that deposits were already being taken for the tractors. Concurrently, Peterbilt Motors Co. is also preparing to launch a fuel cell configuration of its Model 579 tractor, pending readiness of infrastructure and customer demand. The hydrogen fuel cells supplied by Toyota are expected to undergo upgrades, with a third-generation system anticipated to be deployed as early as 2026, promising improvements in durability, fuel efficiency, and cost. Currently, Hyundai is the only manufacturer providing Class 8 hydrogen fuel cell tractors in North America, with Benore Logistic Systems operating 14 Hyundai Xcient tractors on dedicated routes to support a battery cell manufacturing plant in South Carolina.</t>
+  </si>
+  <si>
+    <t>Kenworth Truck Co.; Paccar; Toyota; Peterbilt Motors Co.; Hyundai; Benore Logistic Systems; Lucid Group Inc.; Nikola; Hyzon</t>
+  </si>
+  <si>
+    <t>2023-04-08 (completed): Announcement of delay in production start for hydrogen fuel cell T680 | 2023-04-10 (completed): Peterbilt confirms readiness contingent on infrastructure and customer demand | 2025-01-01 (planned): Initial planned start of serial production for hydrogen fuel cell T680 | 2026-12-31 (target): Target for deployment of third-generation hydrogen fuel cells by Toyota</t>
+  </si>
+  <si>
+    <t>Mount Vernon, Washington; Denton, Texas; Greer, South Carolina; Coolidge, Arizona</t>
+  </si>
+  <si>
+    <t>Kenworth; PACCAR; Hyundai XCIENT; Toyota; Peterbilt</t>
+  </si>
+  <si>
+    <t>range; miles; refueling time; fuel cell</t>
+  </si>
+  <si>
+    <t>https://www.energy.ca.gov/filebrowser/download/7687?fid=7687</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>ERROR: object of type 'NoneType' has no len()</t>
+  </si>
+  <si>
+    <t>PEM</t>
+  </si>
+  <si>
+    <t>California Energy Commission; CEC; EPA</t>
+  </si>
+  <si>
+    <t>MW; kW; km</t>
+  </si>
+  <si>
+    <t>https://www.wastedive.com/news/hydrogen-fuel-cell-refuse-hauler-manufacturing-fleet-wasteexpo/747733/</t>
+  </si>
+  <si>
+    <t>Truck manufacturers are optimistic about hydrogen-powered refuse vehicles despite the dissolution of Hyzon, which conducted the first U.S. pilot for such vehicles in 2022. New Way Trucks, in partnership with Hyzon, plans to deliver the first hydrogen fuel cell-powered refuse hauling vehicle in 2024, with orders already being received. The trucks have shown performance comparable to diesel-powered trucks in pilot tests conducted by companies like Recology and GreenWaste. However, Hyzon's liquidation in December 2022 has raised concerns about the future of hydrogen technology in this sector. Other manufacturers, including Kenworth, Paccar, and Toyota, are also exploring hydrogen fuel cell trucks, although production timelines have faced delays. The regulatory landscape is shifting, with funding cuts proposed by the Trump administration for hydrogen research programs initiated under the Biden administration. Despite these challenges, manufacturers remain committed to developing hydrogen fuel cell vehicles, driven by demand from sustainability-focused customers. The adoption of battery-electric vehicles is also increasing, with 19 new registrations in the previous year, indicating a growing interest in alternative fuel technologies. The key challenge remains the development of hydrogen fueling infrastructure, which is essential for widespread adoption.</t>
+  </si>
+  <si>
+    <t>Hyzon; New Way Trucks; Recology; GreenWaste; Kenworth; Paccar; Toyota; Hyundai; Volvo Group; Daimler; Peterbilt Motors; Oshkosh Corp; Republic Services; Informa</t>
+  </si>
+  <si>
+    <t>2022 (completed): Hyzon conducts the first U.S. pilot for hydrogen-powered refuse vehicles | 2024 (planned): New Way Trucks to deliver the first hydrogen fuel cell-powered refuse hauling vehicle | 2022-12 (completed): Hyzon's board votes to liquidate and dissolve the company | 2023 (expected): Kenworth set to begin production of hydrogen fuel cell truck</t>
+  </si>
+  <si>
+    <t>United States; California</t>
+  </si>
+  <si>
+    <t>heavy-duty vehicle; advanced clean trucks; ACT; BET</t>
+  </si>
+  <si>
+    <t>Kenworth; PACCAR; Toyota; Peterbilt</t>
+  </si>
+  <si>
+    <t>funding; fuel cell</t>
+  </si>
+  <si>
+    <t>https://savageco.com/press-release/savage-and-symbio-north-america-announce-strategic-collaboration-to-kick-off-the-rollout-of-hydrogen-fuel-cell-vehicles-for-drayage/</t>
+  </si>
+  <si>
+    <t>2025-04-28</t>
+  </si>
+  <si>
+    <t>On April 28, 2025, Savage Companies and Symbio North America announced a strategic collaboration to introduce hydrogen fuel cell vehicles (FCEVs) for drayage operations at the 2025 Advanced Clean Transportation Expo in Anaheim, California. The collaboration features a fully developed hydrogen fuel cell powertrain solution engineered by Symbio, which includes a multi-system fuel cell delivering a combined power output of 300 kilowatts, utilizing multiple StackPack™ 75 kW units for enhanced integration. The hydrogen storage solution is provided by FORVIA, featuring 70MPa XL-Tanks with a maximum storage capacity of 34 kilograms of hydrogen, allowing for full-shift operation without refueling. The FCEV driveline prototype is based on a Mack Anthem chassis, supporting the transition of Savage’s fleet of over 80 trucks in California to zero-emission vehicles (ZEVs). The partnership aims to optimize the total cost of ownership (TCO) through lower maintenance requirements and rapid hydrogen refueling in under 15 minutes, enabling 24/7 fleet operation. The collaboration also emphasizes operational data sharing to enhance vehicle efficiency and reliability in real-world applications.</t>
+  </si>
+  <si>
+    <t>Savage Companies; Symbio North America; FORVIA</t>
+  </si>
+  <si>
+    <t>2025-04-28 (completed): Announcement of collaboration at ACT Expo | 2025 (planned): Development of 4×2 FCEV driveline prototype based on Mack Anthem chassis | 2030 (target): Ambition to produce 200,000 StackPack™ per year</t>
+  </si>
+  <si>
+    <t>Temecula, California; Anaheim, California; Midvale, Utah; U.S.; Canada; Mexico; Saudi Arabia</t>
+  </si>
+  <si>
+    <t>clean mobility; sustainable transport; hydrogen mobility; hydrogen storage</t>
+  </si>
+  <si>
+    <t>fleet transition; ACT; BET; FCEV</t>
+  </si>
+  <si>
+    <t>Symbio</t>
+  </si>
+  <si>
+    <t>2025; 2030; deployment; roadmap; milestone</t>
+  </si>
+  <si>
+    <t>kW; investment; capacity; range; kilometers; miles; fuel cell</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,7 +1539,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -84,12 +1547,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -395,52 +1879,2786 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:X63"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="255.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="255.77734375" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>10</v>
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N2" t="s">
+        <v>34</v>
+      </c>
+      <c r="V2" t="s">
+        <v>35</v>
+      </c>
+      <c r="W2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N3" t="s">
+        <v>34</v>
+      </c>
+      <c r="V3" t="s">
+        <v>47</v>
+      </c>
+      <c r="W3" t="s">
+        <v>48</v>
+      </c>
+      <c r="X3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" t="s">
+        <v>57</v>
+      </c>
+      <c r="N5" t="s">
+        <v>34</v>
+      </c>
+      <c r="W5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" t="s">
+        <v>63</v>
+      </c>
+      <c r="I6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N6" t="s">
+        <v>34</v>
+      </c>
+      <c r="W6" t="s">
+        <v>58</v>
+      </c>
+      <c r="X6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" t="s">
+        <v>70</v>
+      </c>
+      <c r="M7" t="s">
+        <v>71</v>
+      </c>
+      <c r="N7" t="s">
+        <v>34</v>
+      </c>
+      <c r="W7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I8" t="s">
+        <v>76</v>
+      </c>
+      <c r="J8" t="s">
+        <v>77</v>
+      </c>
+      <c r="L8" t="s">
+        <v>78</v>
+      </c>
+      <c r="N8" t="s">
+        <v>79</v>
+      </c>
+      <c r="V8" t="s">
+        <v>80</v>
+      </c>
+      <c r="W8" t="s">
+        <v>81</v>
+      </c>
+      <c r="X8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9" t="s">
+        <v>88</v>
+      </c>
+      <c r="L9" t="s">
+        <v>89</v>
+      </c>
+      <c r="M9" t="s">
+        <v>71</v>
+      </c>
+      <c r="N9" t="s">
+        <v>34</v>
+      </c>
+      <c r="W9" t="s">
+        <v>58</v>
+      </c>
+      <c r="X9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I10" t="s">
+        <v>94</v>
+      </c>
+      <c r="J10" t="s">
+        <v>95</v>
+      </c>
+      <c r="L10" t="s">
+        <v>96</v>
+      </c>
+      <c r="M10" t="s">
+        <v>97</v>
+      </c>
+      <c r="N10" t="s">
+        <v>34</v>
+      </c>
+      <c r="P10" t="s">
+        <v>98</v>
+      </c>
+      <c r="R10" t="s">
+        <v>99</v>
+      </c>
+      <c r="V10" t="s">
+        <v>80</v>
+      </c>
+      <c r="W10" t="s">
+        <v>58</v>
+      </c>
+      <c r="X10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H12" t="s">
+        <v>105</v>
+      </c>
+      <c r="I12" t="s">
+        <v>106</v>
+      </c>
+      <c r="L12" t="s">
+        <v>107</v>
+      </c>
+      <c r="N12" t="s">
+        <v>34</v>
+      </c>
+      <c r="W12" t="s">
+        <v>58</v>
+      </c>
+      <c r="X12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H13" t="s">
+        <v>110</v>
+      </c>
+      <c r="I13" t="s">
+        <v>111</v>
+      </c>
+      <c r="J13" t="s">
+        <v>112</v>
+      </c>
+      <c r="L13" t="s">
+        <v>113</v>
+      </c>
+      <c r="N13" t="s">
+        <v>79</v>
+      </c>
+      <c r="P13" t="s">
+        <v>98</v>
+      </c>
+      <c r="R13" t="s">
+        <v>114</v>
+      </c>
+      <c r="V13" t="s">
+        <v>115</v>
+      </c>
+      <c r="W13" t="s">
+        <v>116</v>
+      </c>
+      <c r="X13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" t="s">
+        <v>119</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="H14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I14" t="s">
+        <v>122</v>
+      </c>
+      <c r="J14" t="s">
+        <v>123</v>
+      </c>
+      <c r="L14" t="s">
+        <v>124</v>
+      </c>
+      <c r="N14" t="s">
+        <v>34</v>
+      </c>
+      <c r="P14" t="s">
+        <v>125</v>
+      </c>
+      <c r="T14" t="s">
+        <v>126</v>
+      </c>
+      <c r="W14" t="s">
+        <v>127</v>
+      </c>
+      <c r="X14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H15" t="s">
+        <v>131</v>
+      </c>
+      <c r="I15" t="s">
+        <v>132</v>
+      </c>
+      <c r="N15" t="s">
+        <v>34</v>
+      </c>
+      <c r="T15" t="s">
+        <v>133</v>
+      </c>
+      <c r="W15" t="s">
+        <v>58</v>
+      </c>
+      <c r="X15" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" t="s">
+        <v>136</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H16" t="s">
+        <v>138</v>
+      </c>
+      <c r="I16" t="s">
+        <v>139</v>
+      </c>
+      <c r="L16" t="s">
+        <v>140</v>
+      </c>
+      <c r="N16" t="s">
+        <v>79</v>
+      </c>
+      <c r="T16" t="s">
+        <v>133</v>
+      </c>
+      <c r="W16" t="s">
+        <v>141</v>
+      </c>
+      <c r="X16" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>143</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H17" t="s">
+        <v>145</v>
+      </c>
+      <c r="I17" t="s">
+        <v>146</v>
+      </c>
+      <c r="J17" t="s">
+        <v>147</v>
+      </c>
+      <c r="L17" t="s">
+        <v>33</v>
+      </c>
+      <c r="X17" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>149</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="H18" t="s">
+        <v>151</v>
+      </c>
+      <c r="I18" t="s">
+        <v>152</v>
+      </c>
+      <c r="J18" t="s">
+        <v>153</v>
+      </c>
+      <c r="L18" t="s">
+        <v>33</v>
+      </c>
+      <c r="N18" t="s">
+        <v>34</v>
+      </c>
+      <c r="T18" t="s">
+        <v>154</v>
+      </c>
+      <c r="W18" t="s">
+        <v>58</v>
+      </c>
+      <c r="X18" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>156</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" t="s">
+        <v>157</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H19" t="s">
+        <v>159</v>
+      </c>
+      <c r="I19" t="s">
+        <v>160</v>
+      </c>
+      <c r="J19" t="s">
+        <v>161</v>
+      </c>
+      <c r="L19" t="s">
+        <v>162</v>
+      </c>
+      <c r="N19" t="s">
+        <v>34</v>
+      </c>
+      <c r="P19" t="s">
+        <v>163</v>
+      </c>
+      <c r="T19" t="s">
+        <v>164</v>
+      </c>
+      <c r="V19" t="s">
+        <v>80</v>
+      </c>
+      <c r="W19" t="s">
+        <v>58</v>
+      </c>
+      <c r="X19" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>166</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" t="s">
+        <v>167</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H20" t="s">
+        <v>169</v>
+      </c>
+      <c r="I20" t="s">
+        <v>170</v>
+      </c>
+      <c r="J20" t="s">
+        <v>171</v>
+      </c>
+      <c r="L20" t="s">
+        <v>172</v>
+      </c>
+      <c r="N20" t="s">
+        <v>34</v>
+      </c>
+      <c r="T20" t="s">
+        <v>173</v>
+      </c>
+      <c r="W20" t="s">
+        <v>174</v>
+      </c>
+      <c r="X20" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>176</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H21" t="s">
+        <v>178</v>
+      </c>
+      <c r="I21" t="s">
+        <v>179</v>
+      </c>
+      <c r="J21" t="s">
+        <v>171</v>
+      </c>
+      <c r="L21" t="s">
+        <v>180</v>
+      </c>
+      <c r="N21" t="s">
+        <v>34</v>
+      </c>
+      <c r="P21" t="s">
+        <v>181</v>
+      </c>
+      <c r="V21" t="s">
+        <v>182</v>
+      </c>
+      <c r="X21" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>183</v>
+      </c>
+      <c r="B22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" t="s">
+        <v>184</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H22" t="s">
+        <v>186</v>
+      </c>
+      <c r="I22" t="s">
+        <v>187</v>
+      </c>
+      <c r="J22" t="s">
+        <v>188</v>
+      </c>
+      <c r="L22" t="s">
+        <v>33</v>
+      </c>
+      <c r="N22" t="s">
+        <v>34</v>
+      </c>
+      <c r="P22" t="s">
+        <v>98</v>
+      </c>
+      <c r="T22" t="s">
+        <v>186</v>
+      </c>
+      <c r="V22" t="s">
+        <v>35</v>
+      </c>
+      <c r="W22" t="s">
+        <v>189</v>
+      </c>
+      <c r="X22" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>191</v>
+      </c>
+      <c r="B23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" t="s">
+        <v>192</v>
+      </c>
+      <c r="E23" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" t="s">
+        <v>193</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="H23" t="s">
+        <v>195</v>
+      </c>
+      <c r="I23" t="s">
+        <v>196</v>
+      </c>
+      <c r="J23" t="s">
+        <v>197</v>
+      </c>
+      <c r="L23" t="s">
+        <v>198</v>
+      </c>
+      <c r="N23" t="s">
+        <v>34</v>
+      </c>
+      <c r="P23" t="s">
+        <v>98</v>
+      </c>
+      <c r="V23" t="s">
+        <v>182</v>
+      </c>
+      <c r="W23" t="s">
+        <v>199</v>
+      </c>
+      <c r="X23" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>200</v>
+      </c>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" t="s">
+        <v>192</v>
+      </c>
+      <c r="E24" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" t="s">
+        <v>201</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="H24" t="s">
+        <v>203</v>
+      </c>
+      <c r="I24" t="s">
+        <v>204</v>
+      </c>
+      <c r="J24" t="s">
+        <v>205</v>
+      </c>
+      <c r="L24" t="s">
+        <v>206</v>
+      </c>
+      <c r="N24" t="s">
+        <v>34</v>
+      </c>
+      <c r="W24" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>207</v>
+      </c>
+      <c r="B25" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>208</v>
+      </c>
+      <c r="B26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" t="s">
+        <v>209</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="H26" t="s">
+        <v>211</v>
+      </c>
+      <c r="I26" t="s">
+        <v>212</v>
+      </c>
+      <c r="J26" t="s">
+        <v>213</v>
+      </c>
+      <c r="L26" t="s">
+        <v>214</v>
+      </c>
+      <c r="N26" t="s">
+        <v>34</v>
+      </c>
+      <c r="W26" t="s">
+        <v>58</v>
+      </c>
+      <c r="X26" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>215</v>
+      </c>
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" t="s">
+        <v>216</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="H27" t="s">
+        <v>218</v>
+      </c>
+      <c r="I27" t="s">
+        <v>219</v>
+      </c>
+      <c r="J27" t="s">
+        <v>220</v>
+      </c>
+      <c r="L27" t="s">
+        <v>221</v>
+      </c>
+      <c r="N27" t="s">
+        <v>34</v>
+      </c>
+      <c r="V27" t="s">
+        <v>80</v>
+      </c>
+      <c r="W27" t="s">
+        <v>222</v>
+      </c>
+      <c r="X27" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>223</v>
+      </c>
+      <c r="B28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" t="s">
+        <v>192</v>
+      </c>
+      <c r="E28" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" t="s">
+        <v>224</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="H28" t="s">
+        <v>226</v>
+      </c>
+      <c r="I28" t="s">
+        <v>227</v>
+      </c>
+      <c r="J28" t="s">
+        <v>228</v>
+      </c>
+      <c r="L28" t="s">
+        <v>124</v>
+      </c>
+      <c r="N28" t="s">
+        <v>34</v>
+      </c>
+      <c r="P28" t="s">
+        <v>98</v>
+      </c>
+      <c r="V28" t="s">
+        <v>80</v>
+      </c>
+      <c r="W28" t="s">
+        <v>229</v>
+      </c>
+      <c r="X28" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>231</v>
+      </c>
+      <c r="B29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D29" t="s">
+        <v>192</v>
+      </c>
+      <c r="E29" t="s">
+        <v>39</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="H29" t="s">
+        <v>233</v>
+      </c>
+      <c r="I29" t="s">
+        <v>234</v>
+      </c>
+      <c r="J29" t="s">
+        <v>235</v>
+      </c>
+      <c r="L29" t="s">
+        <v>96</v>
+      </c>
+      <c r="O29" t="s">
+        <v>236</v>
+      </c>
+      <c r="P29" t="s">
+        <v>98</v>
+      </c>
+      <c r="V29" t="s">
+        <v>182</v>
+      </c>
+      <c r="W29" t="s">
+        <v>237</v>
+      </c>
+      <c r="X29" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>238</v>
+      </c>
+      <c r="B30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F30" t="s">
+        <v>239</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="H30" t="s">
+        <v>241</v>
+      </c>
+      <c r="I30" t="s">
+        <v>242</v>
+      </c>
+      <c r="J30" t="s">
+        <v>243</v>
+      </c>
+      <c r="L30" t="s">
+        <v>96</v>
+      </c>
+      <c r="P30" t="s">
+        <v>98</v>
+      </c>
+      <c r="S30" t="s">
+        <v>244</v>
+      </c>
+      <c r="U30" t="s">
+        <v>245</v>
+      </c>
+      <c r="V30" t="s">
+        <v>80</v>
+      </c>
+      <c r="W30" t="s">
+        <v>36</v>
+      </c>
+      <c r="X30" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>247</v>
+      </c>
+      <c r="B31" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" t="s">
+        <v>39</v>
+      </c>
+      <c r="F31" t="s">
+        <v>248</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="H31" t="s">
+        <v>250</v>
+      </c>
+      <c r="I31" t="s">
+        <v>251</v>
+      </c>
+      <c r="J31" t="s">
+        <v>252</v>
+      </c>
+      <c r="L31" t="s">
+        <v>253</v>
+      </c>
+      <c r="N31" t="s">
+        <v>34</v>
+      </c>
+      <c r="W31" t="s">
+        <v>58</v>
+      </c>
+      <c r="X31" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>254</v>
+      </c>
+      <c r="B32" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" t="s">
+        <v>192</v>
+      </c>
+      <c r="E32" t="s">
+        <v>39</v>
+      </c>
+      <c r="F32" t="s">
+        <v>255</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H32" t="s">
+        <v>257</v>
+      </c>
+      <c r="I32" t="s">
+        <v>258</v>
+      </c>
+      <c r="N32" t="s">
+        <v>34</v>
+      </c>
+      <c r="W32" t="s">
+        <v>58</v>
+      </c>
+      <c r="X32" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>259</v>
+      </c>
+      <c r="B33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" t="s">
+        <v>192</v>
+      </c>
+      <c r="E33" t="s">
+        <v>39</v>
+      </c>
+      <c r="F33" t="s">
+        <v>260</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="I33" t="s">
+        <v>262</v>
+      </c>
+      <c r="J33" t="s">
+        <v>263</v>
+      </c>
+      <c r="N33" t="s">
+        <v>34</v>
+      </c>
+      <c r="W33" t="s">
+        <v>58</v>
+      </c>
+      <c r="X33" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>264</v>
+      </c>
+      <c r="B34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" t="s">
+        <v>39</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="H34" t="s">
+        <v>266</v>
+      </c>
+      <c r="I34" t="s">
+        <v>267</v>
+      </c>
+      <c r="J34" t="s">
+        <v>268</v>
+      </c>
+      <c r="L34" t="s">
+        <v>269</v>
+      </c>
+      <c r="N34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>270</v>
+      </c>
+      <c r="B35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" t="s">
+        <v>39</v>
+      </c>
+      <c r="F35" t="s">
+        <v>28</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="H35" t="s">
+        <v>272</v>
+      </c>
+      <c r="I35" t="s">
+        <v>273</v>
+      </c>
+      <c r="J35" t="s">
+        <v>274</v>
+      </c>
+      <c r="L35" t="s">
+        <v>275</v>
+      </c>
+      <c r="N35" t="s">
+        <v>79</v>
+      </c>
+      <c r="W35" t="s">
+        <v>58</v>
+      </c>
+      <c r="X35" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>276</v>
+      </c>
+      <c r="B36" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" t="s">
+        <v>39</v>
+      </c>
+      <c r="F36" t="s">
+        <v>216</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="H36" t="s">
+        <v>278</v>
+      </c>
+      <c r="I36" t="s">
+        <v>279</v>
+      </c>
+      <c r="J36" t="s">
+        <v>280</v>
+      </c>
+      <c r="L36" t="s">
+        <v>33</v>
+      </c>
+      <c r="N36" t="s">
+        <v>34</v>
+      </c>
+      <c r="W36" t="s">
+        <v>281</v>
+      </c>
+      <c r="X36" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>283</v>
+      </c>
+      <c r="B37" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" t="s">
+        <v>26</v>
+      </c>
+      <c r="D37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" t="s">
+        <v>39</v>
+      </c>
+      <c r="F37" t="s">
+        <v>284</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="H37" t="s">
+        <v>286</v>
+      </c>
+      <c r="I37" t="s">
+        <v>287</v>
+      </c>
+      <c r="J37" t="s">
+        <v>171</v>
+      </c>
+      <c r="N37" t="s">
+        <v>34</v>
+      </c>
+      <c r="P37" t="s">
+        <v>288</v>
+      </c>
+      <c r="T37" t="s">
+        <v>133</v>
+      </c>
+      <c r="W37" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>289</v>
+      </c>
+      <c r="B38" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" t="s">
+        <v>26</v>
+      </c>
+      <c r="D38" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" t="s">
+        <v>39</v>
+      </c>
+      <c r="F38" t="s">
+        <v>28</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="H38" t="s">
+        <v>291</v>
+      </c>
+      <c r="I38" t="s">
+        <v>292</v>
+      </c>
+      <c r="J38" t="s">
+        <v>293</v>
+      </c>
+      <c r="L38" t="s">
+        <v>294</v>
+      </c>
+      <c r="N38" t="s">
+        <v>34</v>
+      </c>
+      <c r="P38" t="s">
+        <v>288</v>
+      </c>
+      <c r="T38" t="s">
+        <v>133</v>
+      </c>
+      <c r="W38" t="s">
+        <v>295</v>
+      </c>
+      <c r="X38" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>297</v>
+      </c>
+      <c r="B39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39" t="s">
+        <v>39</v>
+      </c>
+      <c r="F39" t="s">
+        <v>298</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="H39" t="s">
+        <v>300</v>
+      </c>
+      <c r="I39" t="s">
+        <v>301</v>
+      </c>
+      <c r="L39" t="s">
+        <v>302</v>
+      </c>
+      <c r="N39" t="s">
+        <v>79</v>
+      </c>
+      <c r="P39" t="s">
+        <v>303</v>
+      </c>
+      <c r="V39" t="s">
+        <v>304</v>
+      </c>
+      <c r="W39" t="s">
+        <v>305</v>
+      </c>
+      <c r="X39" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>307</v>
+      </c>
+      <c r="B40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" t="s">
+        <v>26</v>
+      </c>
+      <c r="D40" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" t="s">
+        <v>39</v>
+      </c>
+      <c r="F40" t="s">
+        <v>216</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="H40" t="s">
+        <v>309</v>
+      </c>
+      <c r="I40" t="s">
+        <v>310</v>
+      </c>
+      <c r="J40" t="s">
+        <v>311</v>
+      </c>
+      <c r="L40" t="s">
+        <v>312</v>
+      </c>
+      <c r="N40" t="s">
+        <v>34</v>
+      </c>
+      <c r="P40" t="s">
+        <v>98</v>
+      </c>
+      <c r="U40" t="s">
+        <v>245</v>
+      </c>
+      <c r="V40" t="s">
+        <v>35</v>
+      </c>
+      <c r="W40" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>314</v>
+      </c>
+      <c r="B41" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" t="s">
+        <v>26</v>
+      </c>
+      <c r="D41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" t="s">
+        <v>27</v>
+      </c>
+      <c r="F41" t="s">
+        <v>315</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H41" t="s">
+        <v>317</v>
+      </c>
+      <c r="I41" t="s">
+        <v>318</v>
+      </c>
+      <c r="J41" t="s">
+        <v>319</v>
+      </c>
+      <c r="M41" t="s">
+        <v>320</v>
+      </c>
+      <c r="N41" t="s">
+        <v>34</v>
+      </c>
+      <c r="W41" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>321</v>
+      </c>
+      <c r="B42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C42" t="s">
+        <v>26</v>
+      </c>
+      <c r="D42" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" t="s">
+        <v>39</v>
+      </c>
+      <c r="F42" t="s">
+        <v>216</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="H42" t="s">
+        <v>323</v>
+      </c>
+      <c r="I42" t="s">
+        <v>324</v>
+      </c>
+      <c r="J42" t="s">
+        <v>325</v>
+      </c>
+      <c r="L42" t="s">
+        <v>326</v>
+      </c>
+      <c r="M42" t="s">
+        <v>320</v>
+      </c>
+      <c r="N42" t="s">
+        <v>34</v>
+      </c>
+      <c r="V42" t="s">
+        <v>35</v>
+      </c>
+      <c r="W42" t="s">
+        <v>327</v>
+      </c>
+      <c r="X42" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>329</v>
+      </c>
+      <c r="B43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" t="s">
+        <v>26</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" t="s">
+        <v>27</v>
+      </c>
+      <c r="F43" t="s">
+        <v>330</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="H43" t="s">
+        <v>332</v>
+      </c>
+      <c r="I43" t="s">
+        <v>333</v>
+      </c>
+      <c r="J43" t="s">
+        <v>334</v>
+      </c>
+      <c r="L43" t="s">
+        <v>33</v>
+      </c>
+      <c r="M43" t="s">
+        <v>335</v>
+      </c>
+      <c r="P43" t="s">
+        <v>98</v>
+      </c>
+      <c r="W43" t="s">
+        <v>336</v>
+      </c>
+      <c r="X43" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>338</v>
+      </c>
+      <c r="B44" t="s">
+        <v>25</v>
+      </c>
+      <c r="C44" t="s">
+        <v>26</v>
+      </c>
+      <c r="D44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" t="s">
+        <v>27</v>
+      </c>
+      <c r="F44" t="s">
+        <v>216</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="H44" t="s">
+        <v>340</v>
+      </c>
+      <c r="I44" t="s">
+        <v>341</v>
+      </c>
+      <c r="J44" t="s">
+        <v>342</v>
+      </c>
+      <c r="L44" t="s">
+        <v>343</v>
+      </c>
+      <c r="M44" t="s">
+        <v>320</v>
+      </c>
+      <c r="N44" t="s">
+        <v>34</v>
+      </c>
+      <c r="P44" t="s">
+        <v>98</v>
+      </c>
+      <c r="U44" t="s">
+        <v>245</v>
+      </c>
+      <c r="V44" t="s">
+        <v>80</v>
+      </c>
+      <c r="W44" t="s">
+        <v>344</v>
+      </c>
+      <c r="X44" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>346</v>
+      </c>
+      <c r="B45" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" t="s">
+        <v>26</v>
+      </c>
+      <c r="D45" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" t="s">
+        <v>27</v>
+      </c>
+      <c r="F45" t="s">
+        <v>216</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="H45" t="s">
+        <v>348</v>
+      </c>
+      <c r="I45" t="s">
+        <v>349</v>
+      </c>
+      <c r="J45" t="s">
+        <v>350</v>
+      </c>
+      <c r="L45" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>353</v>
+      </c>
+      <c r="B46" t="s">
+        <v>25</v>
+      </c>
+      <c r="C46" t="s">
+        <v>26</v>
+      </c>
+      <c r="D46" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" t="s">
+        <v>60</v>
+      </c>
+      <c r="F46" t="s">
+        <v>354</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="H46" t="s">
+        <v>356</v>
+      </c>
+      <c r="I46" t="s">
+        <v>357</v>
+      </c>
+      <c r="J46" t="s">
+        <v>358</v>
+      </c>
+      <c r="L46" t="s">
+        <v>89</v>
+      </c>
+      <c r="M46" t="s">
+        <v>71</v>
+      </c>
+      <c r="N46" t="s">
+        <v>34</v>
+      </c>
+      <c r="W46" t="s">
+        <v>58</v>
+      </c>
+      <c r="X46" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>359</v>
+      </c>
+      <c r="B47" t="s">
+        <v>25</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47" t="s">
+        <v>27</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="I47" t="s">
+        <v>361</v>
+      </c>
+      <c r="J47" t="s">
+        <v>362</v>
+      </c>
+      <c r="L47" t="s">
+        <v>363</v>
+      </c>
+      <c r="M47" t="s">
+        <v>364</v>
+      </c>
+      <c r="N47" t="s">
+        <v>365</v>
+      </c>
+      <c r="P47" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>366</v>
+      </c>
+      <c r="T47" t="s">
+        <v>367</v>
+      </c>
+      <c r="U47" t="s">
+        <v>245</v>
+      </c>
+      <c r="V47" t="s">
+        <v>182</v>
+      </c>
+      <c r="W47" t="s">
+        <v>368</v>
+      </c>
+      <c r="X47" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>370</v>
+      </c>
+      <c r="B48" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" t="s">
+        <v>26</v>
+      </c>
+      <c r="D48" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" t="s">
+        <v>60</v>
+      </c>
+      <c r="F48" t="s">
+        <v>216</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="H48" t="s">
+        <v>372</v>
+      </c>
+      <c r="I48" t="s">
+        <v>373</v>
+      </c>
+      <c r="J48" t="s">
+        <v>374</v>
+      </c>
+      <c r="L48" t="s">
+        <v>375</v>
+      </c>
+      <c r="M48" t="s">
+        <v>71</v>
+      </c>
+      <c r="N48" t="s">
+        <v>79</v>
+      </c>
+      <c r="P48" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>376</v>
+      </c>
+      <c r="W48" t="s">
+        <v>174</v>
+      </c>
+      <c r="X48" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>378</v>
+      </c>
+      <c r="B49" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" t="s">
+        <v>26</v>
+      </c>
+      <c r="D49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49" t="s">
+        <v>60</v>
+      </c>
+      <c r="F49" t="s">
+        <v>216</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="H49" t="s">
+        <v>380</v>
+      </c>
+      <c r="I49" t="s">
+        <v>381</v>
+      </c>
+      <c r="J49" t="s">
+        <v>382</v>
+      </c>
+      <c r="L49" t="s">
+        <v>383</v>
+      </c>
+      <c r="M49" t="s">
+        <v>384</v>
+      </c>
+      <c r="N49" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>385</v>
+      </c>
+      <c r="V49" t="s">
+        <v>386</v>
+      </c>
+      <c r="X49" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>388</v>
+      </c>
+      <c r="B50" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" t="s">
+        <v>26</v>
+      </c>
+      <c r="D50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" t="s">
+        <v>389</v>
+      </c>
+      <c r="F50" t="s">
+        <v>216</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="H50" t="s">
+        <v>391</v>
+      </c>
+      <c r="I50" t="s">
+        <v>392</v>
+      </c>
+      <c r="J50" t="s">
+        <v>393</v>
+      </c>
+      <c r="L50" t="s">
+        <v>394</v>
+      </c>
+      <c r="M50" t="s">
+        <v>395</v>
+      </c>
+      <c r="R50" t="s">
+        <v>99</v>
+      </c>
+      <c r="U50" t="s">
+        <v>396</v>
+      </c>
+      <c r="V50" t="s">
+        <v>386</v>
+      </c>
+      <c r="W50" t="s">
+        <v>397</v>
+      </c>
+      <c r="X50" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>398</v>
+      </c>
+      <c r="B51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" t="s">
+        <v>26</v>
+      </c>
+      <c r="D51" t="s">
+        <v>12</v>
+      </c>
+      <c r="E51" t="s">
+        <v>39</v>
+      </c>
+      <c r="F51" t="s">
+        <v>399</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="H51" t="s">
+        <v>401</v>
+      </c>
+      <c r="I51" t="s">
+        <v>402</v>
+      </c>
+      <c r="J51" t="s">
+        <v>403</v>
+      </c>
+      <c r="L51" t="s">
+        <v>404</v>
+      </c>
+      <c r="M51" t="s">
+        <v>320</v>
+      </c>
+      <c r="N51" t="s">
+        <v>34</v>
+      </c>
+      <c r="V51" t="s">
+        <v>80</v>
+      </c>
+      <c r="W51" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>405</v>
+      </c>
+      <c r="B52" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52" t="s">
+        <v>26</v>
+      </c>
+      <c r="D52" t="s">
+        <v>192</v>
+      </c>
+      <c r="E52" t="s">
+        <v>39</v>
+      </c>
+      <c r="F52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="H52" t="s">
+        <v>407</v>
+      </c>
+      <c r="I52" t="s">
+        <v>408</v>
+      </c>
+      <c r="J52" t="s">
+        <v>409</v>
+      </c>
+      <c r="V52" t="s">
+        <v>80</v>
+      </c>
+      <c r="X52" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>410</v>
+      </c>
+      <c r="B53" t="s">
+        <v>25</v>
+      </c>
+      <c r="C53" t="s">
+        <v>26</v>
+      </c>
+      <c r="D53" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" t="s">
+        <v>39</v>
+      </c>
+      <c r="F53" t="s">
+        <v>411</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="H53" t="s">
+        <v>413</v>
+      </c>
+      <c r="I53" t="s">
+        <v>414</v>
+      </c>
+      <c r="J53" t="s">
+        <v>415</v>
+      </c>
+      <c r="L53" t="s">
+        <v>416</v>
+      </c>
+      <c r="N53" t="s">
+        <v>34</v>
+      </c>
+      <c r="W53" t="s">
+        <v>58</v>
+      </c>
+      <c r="X53" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>417</v>
+      </c>
+      <c r="B54" t="s">
+        <v>25</v>
+      </c>
+      <c r="C54" t="s">
+        <v>26</v>
+      </c>
+      <c r="D54" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" t="s">
+        <v>39</v>
+      </c>
+      <c r="F54" t="s">
+        <v>28</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="H54" t="s">
+        <v>419</v>
+      </c>
+      <c r="I54" t="s">
+        <v>420</v>
+      </c>
+      <c r="J54" t="s">
+        <v>421</v>
+      </c>
+      <c r="L54" t="s">
+        <v>422</v>
+      </c>
+      <c r="N54" t="s">
+        <v>34</v>
+      </c>
+      <c r="R54" t="s">
+        <v>114</v>
+      </c>
+      <c r="V54" t="s">
+        <v>80</v>
+      </c>
+      <c r="W54" t="s">
+        <v>423</v>
+      </c>
+      <c r="X54" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>425</v>
+      </c>
+      <c r="B55" t="s">
+        <v>25</v>
+      </c>
+      <c r="D55" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" t="s">
+        <v>39</v>
+      </c>
+      <c r="F55" t="s">
+        <v>426</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="H55" t="s">
+        <v>428</v>
+      </c>
+      <c r="I55" t="s">
+        <v>429</v>
+      </c>
+      <c r="J55" t="s">
+        <v>430</v>
+      </c>
+      <c r="N55" t="s">
+        <v>34</v>
+      </c>
+      <c r="W55" t="s">
+        <v>58</v>
+      </c>
+      <c r="X55" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>431</v>
+      </c>
+      <c r="B56" t="s">
+        <v>25</v>
+      </c>
+      <c r="C56" t="s">
+        <v>26</v>
+      </c>
+      <c r="D56" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" t="s">
+        <v>39</v>
+      </c>
+      <c r="F56" t="s">
+        <v>432</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="H56" t="s">
+        <v>434</v>
+      </c>
+      <c r="I56" t="s">
+        <v>435</v>
+      </c>
+      <c r="J56" t="s">
+        <v>57</v>
+      </c>
+      <c r="L56" t="s">
+        <v>89</v>
+      </c>
+      <c r="N56" t="s">
+        <v>34</v>
+      </c>
+      <c r="W56" t="s">
+        <v>58</v>
+      </c>
+      <c r="X56" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>436</v>
+      </c>
+      <c r="B57" t="s">
+        <v>25</v>
+      </c>
+      <c r="C57" t="s">
+        <v>26</v>
+      </c>
+      <c r="D57" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" t="s">
+        <v>39</v>
+      </c>
+      <c r="F57" t="s">
+        <v>437</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="H57" t="s">
+        <v>439</v>
+      </c>
+      <c r="I57" t="s">
+        <v>440</v>
+      </c>
+      <c r="J57" t="s">
+        <v>441</v>
+      </c>
+      <c r="L57" t="s">
+        <v>442</v>
+      </c>
+      <c r="N57" t="s">
+        <v>34</v>
+      </c>
+      <c r="R57" t="s">
+        <v>443</v>
+      </c>
+      <c r="U57" t="s">
+        <v>245</v>
+      </c>
+      <c r="V57" t="s">
+        <v>80</v>
+      </c>
+      <c r="W57" t="s">
+        <v>444</v>
+      </c>
+      <c r="X57" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>446</v>
+      </c>
+      <c r="B58" t="s">
+        <v>25</v>
+      </c>
+      <c r="D58" t="s">
+        <v>192</v>
+      </c>
+      <c r="E58" t="s">
+        <v>39</v>
+      </c>
+      <c r="F58" t="s">
+        <v>447</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="H58" t="s">
+        <v>449</v>
+      </c>
+      <c r="I58" t="s">
+        <v>450</v>
+      </c>
+      <c r="J58" t="s">
+        <v>451</v>
+      </c>
+      <c r="L58" t="s">
+        <v>452</v>
+      </c>
+      <c r="N58" t="s">
+        <v>453</v>
+      </c>
+      <c r="R58" t="s">
+        <v>454</v>
+      </c>
+      <c r="V58" t="s">
+        <v>80</v>
+      </c>
+      <c r="W58" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>456</v>
+      </c>
+      <c r="B59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C59" t="s">
+        <v>26</v>
+      </c>
+      <c r="D59" t="s">
+        <v>192</v>
+      </c>
+      <c r="E59" t="s">
+        <v>39</v>
+      </c>
+      <c r="F59" t="s">
+        <v>216</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="H59" t="s">
+        <v>458</v>
+      </c>
+      <c r="I59" t="s">
+        <v>459</v>
+      </c>
+      <c r="J59" t="s">
+        <v>460</v>
+      </c>
+      <c r="L59" t="s">
+        <v>172</v>
+      </c>
+      <c r="N59" t="s">
+        <v>461</v>
+      </c>
+      <c r="W59" t="s">
+        <v>462</v>
+      </c>
+      <c r="X59" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>464</v>
+      </c>
+      <c r="B60" t="s">
+        <v>25</v>
+      </c>
+      <c r="C60" t="s">
+        <v>26</v>
+      </c>
+      <c r="D60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" t="s">
+        <v>39</v>
+      </c>
+      <c r="F60" t="s">
+        <v>465</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="H60" t="s">
+        <v>467</v>
+      </c>
+      <c r="I60" t="s">
+        <v>468</v>
+      </c>
+      <c r="J60" t="s">
+        <v>469</v>
+      </c>
+      <c r="N60" t="s">
+        <v>79</v>
+      </c>
+      <c r="R60" t="s">
+        <v>470</v>
+      </c>
+      <c r="W60" t="s">
+        <v>455</v>
+      </c>
+      <c r="X60" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>472</v>
+      </c>
+      <c r="B61" t="s">
+        <v>25</v>
+      </c>
+      <c r="D61" t="s">
+        <v>473</v>
+      </c>
+      <c r="E61" t="s">
+        <v>39</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="L61" t="s">
+        <v>475</v>
+      </c>
+      <c r="V61" t="s">
+        <v>476</v>
+      </c>
+      <c r="W61" t="s">
+        <v>58</v>
+      </c>
+      <c r="X61" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>478</v>
+      </c>
+      <c r="B62" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" t="s">
+        <v>26</v>
+      </c>
+      <c r="D62" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" t="s">
+        <v>39</v>
+      </c>
+      <c r="F62" t="s">
+        <v>330</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="H62" t="s">
+        <v>480</v>
+      </c>
+      <c r="I62" t="s">
+        <v>481</v>
+      </c>
+      <c r="J62" t="s">
+        <v>482</v>
+      </c>
+      <c r="L62" t="s">
+        <v>33</v>
+      </c>
+      <c r="N62" t="s">
+        <v>483</v>
+      </c>
+      <c r="R62" t="s">
+        <v>484</v>
+      </c>
+      <c r="W62" t="s">
+        <v>462</v>
+      </c>
+      <c r="X62" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>486</v>
+      </c>
+      <c r="B63" t="s">
+        <v>25</v>
+      </c>
+      <c r="C63" t="s">
+        <v>26</v>
+      </c>
+      <c r="D63" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" t="s">
+        <v>39</v>
+      </c>
+      <c r="F63" t="s">
+        <v>487</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="H63" t="s">
+        <v>489</v>
+      </c>
+      <c r="I63" t="s">
+        <v>490</v>
+      </c>
+      <c r="J63" t="s">
+        <v>491</v>
+      </c>
+      <c r="L63" t="s">
+        <v>492</v>
+      </c>
+      <c r="N63" t="s">
+        <v>493</v>
+      </c>
+      <c r="P63" t="s">
+        <v>98</v>
+      </c>
+      <c r="R63" t="s">
+        <v>494</v>
+      </c>
+      <c r="V63" t="s">
+        <v>80</v>
+      </c>
+      <c r="W63" t="s">
+        <v>495</v>
+      </c>
+      <c r="X63" t="s">
+        <v>496</v>
       </c>
     </row>
   </sheetData>
